--- a/model/Outputs/11. Interest rate/10/Output Files/0.1/Output_18_39.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.1/Output_18_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3694052.091294372</v>
+        <v>3694135.847615197</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17424111.62762229</v>
+        <v>17424111.6276223</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17424111.62762229</v>
+        <v>17424111.6276223</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4036467.593299042</v>
+        <v>4036467.59329904</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4036467.593299042</v>
+        <v>4036467.59329904</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48818732.47780249</v>
+        <v>48818732.47780246</v>
       </c>
     </row>
   </sheetData>
@@ -657,7 +657,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
         <v>10.33915573984979</v>
@@ -708,19 +708,19 @@
         <v>76.89299192292594</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>14.97337755244518</v>
+      </c>
+      <c r="X2" t="n">
         <v>124</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>64.44795579543909</v>
       </c>
       <c r="Y2" t="n">
         <v>111.3174326828064</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>111.535425392244</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>58.73324524763018</v>
       </c>
       <c r="T3" t="n">
-        <v>3.658482198645913</v>
+        <v>115.1939075908898</v>
       </c>
       <c r="U3" t="n">
         <v>0.182623911130122</v>
@@ -857,10 +857,10 @@
         <v>124</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>50.89261168642087</v>
       </c>
       <c r="R4" t="n">
-        <v>50.89261168642087</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>2.969432588523748</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -948,19 +948,19 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>60.20483817079538</v>
+        <v>99.96628168511943</v>
       </c>
       <c r="V5" t="n">
         <v>124</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="X5" t="n">
         <v>124</v>
       </c>
       <c r="Y5" t="n">
-        <v>111.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>106.7997470864971</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>111.535425392244</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>119.2643216942532</v>
       </c>
       <c r="R6" t="n">
         <v>121.0985520093604</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>65.22787369763185</v>
       </c>
       <c r="N7" t="n">
         <v>117.0987146159472</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="P7" t="n">
         <v>124</v>
       </c>
       <c r="Q7" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>116.1204853840528</v>
+        <v>50.89261168642093</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1131,16 +1131,16 @@
         <v>78.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>46.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>1.600945054766743</v>
+        <v>7.339155739849787</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.889628708011855</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>180.2263756984131</v>
+        <v>124.7606684554556</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53.98104656036473</v>
+        <v>263</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>72.00955569064499</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>119.2643216942532</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>263</v>
+        <v>118.0985520093604</v>
       </c>
       <c r="S9" t="n">
         <v>263</v>
@@ -1273,7 +1273,7 @@
         <v>29.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>16.86273944538755</v>
+        <v>263</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1319,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>62.22787369763186</v>
       </c>
       <c r="N10" t="n">
-        <v>65.46172547795341</v>
+        <v>114.0987146159472</v>
       </c>
       <c r="O10" t="n">
         <v>187.4880558822936</v>
@@ -1331,7 +1331,7 @@
         <v>241.7006186397529</v>
       </c>
       <c r="Q10" t="n">
-        <v>263</v>
+        <v>152.1351371643744</v>
       </c>
       <c r="R10" t="n">
         <v>263</v>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43.51020768850297</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>102.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>96.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>91.94017126634148</v>
+        <v>91.94017126634151</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1419,19 +1419,19 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>275.2263756984131</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>324.000000000013</v>
+        <v>324</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>321.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>324.0000000000109</v>
+        <v>324</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>195.5880045668345</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
         <v>31.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>17.31795096936697</v>
+        <v>17.31795096936696</v>
       </c>
       <c r="H12" t="n">
-        <v>20.0964645449117</v>
+        <v>20.09646454491173</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1498,10 +1498,10 @@
         <v>150.7332452476302</v>
       </c>
       <c r="T12" t="n">
-        <v>95.65848219864588</v>
+        <v>95.65848219864591</v>
       </c>
       <c r="U12" t="n">
-        <v>92.18262391113015</v>
+        <v>92.18262391113012</v>
       </c>
       <c r="V12" t="n">
         <v>106.5106671915202</v>
@@ -1553,25 +1553,25 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>63.00034946925458</v>
+        <v>63.00034946925456</v>
       </c>
       <c r="M13" t="n">
-        <v>157.2278736976318</v>
+        <v>157.2278736976319</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>209.0987146159472</v>
       </c>
       <c r="O13" t="n">
-        <v>282.4880558822936</v>
+        <v>282.4880558822937</v>
       </c>
       <c r="P13" t="n">
-        <v>106.6629209508199</v>
+        <v>324</v>
       </c>
       <c r="Q13" t="n">
-        <v>324</v>
+        <v>221.5642063348726</v>
       </c>
       <c r="R13" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1605,22 +1605,22 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>141.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>102.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>96.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>94.96943258852377</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>91.94017126634151</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1656,19 +1656,19 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>275.2263756984131</v>
+        <v>3.246342372508322</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="V14" t="n">
         <v>321.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="X14" t="n">
-        <v>132.6888335890421</v>
+        <v>284.2818334606677</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -1696,10 +1696,10 @@
         <v>31.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>17.31795096936696</v>
+        <v>17.31795096936697</v>
       </c>
       <c r="H15" t="n">
-        <v>20.09646454491173</v>
+        <v>20.0964645449117</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,22 +1729,22 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>211.3499952661064</v>
+        <v>213.0985520093604</v>
       </c>
       <c r="S15" t="n">
         <v>150.7332452476302</v>
       </c>
       <c r="T15" t="n">
-        <v>95.65848219864591</v>
+        <v>95.65848219864588</v>
       </c>
       <c r="U15" t="n">
-        <v>92.18262391113012</v>
+        <v>92.18262391113015</v>
       </c>
       <c r="V15" t="n">
         <v>106.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>124.3731429098285</v>
+        <v>122.6245861665746</v>
       </c>
       <c r="X15" t="n">
         <v>111.8627394453875</v>
@@ -1790,25 +1790,25 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>63.00034946925456</v>
+        <v>63.00034946925458</v>
       </c>
       <c r="M16" t="n">
-        <v>157.2278736976319</v>
+        <v>157.2278736976318</v>
       </c>
       <c r="N16" t="n">
         <v>209.0987146159472</v>
       </c>
       <c r="O16" t="n">
-        <v>282.4880558822937</v>
+        <v>282.4880558822936</v>
       </c>
       <c r="P16" t="n">
         <v>324</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>221.5642063348726</v>
       </c>
       <c r="R16" t="n">
-        <v>221.5642063348726</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1839,13 +1839,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>86.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>54.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>15.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>9.363289606868648</v>
@@ -1896,7 +1896,7 @@
         <v>188.2263756984131</v>
       </c>
       <c r="U17" t="n">
-        <v>203.7423304399191</v>
+        <v>254.1582613727313</v>
       </c>
       <c r="V17" t="n">
         <v>234.8510241668239</v>
@@ -1905,10 +1905,10 @@
         <v>243.3734759809475</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>197.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>116.3174326828064</v>
+        <v>25.43271522774474</v>
       </c>
     </row>
     <row r="18">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>202.6112915517259</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,19 +1972,19 @@
         <v>63.73324524763018</v>
       </c>
       <c r="T18" t="n">
+        <v>8.658482198645913</v>
+      </c>
+      <c r="U18" t="n">
+        <v>141.6503538712872</v>
+      </c>
+      <c r="V18" t="n">
         <v>324</v>
       </c>
-      <c r="U18" t="n">
-        <v>324</v>
-      </c>
-      <c r="V18" t="n">
-        <v>19.51066719152016</v>
-      </c>
       <c r="W18" t="n">
-        <v>324</v>
+        <v>37.37314290982852</v>
       </c>
       <c r="X18" t="n">
-        <v>71.64534278535467</v>
+        <v>24.86273944538755</v>
       </c>
       <c r="Y18" t="n">
         <v>4.391392766134345</v>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>86.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.58184731018156</v>
+        <v>54.47457824299391</v>
       </c>
       <c r="D20" t="n">
         <v>15.33915573984979</v>
@@ -2091,10 +2091,10 @@
         <v>9.889628708011855</v>
       </c>
       <c r="G20" t="n">
-        <v>7.969432588523773</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.940171266341508</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>81.89299192292594</v>
       </c>
       <c r="T20" t="n">
-        <v>188.2263756984131</v>
+        <v>55.96072811537294</v>
       </c>
       <c r="U20" t="n">
         <v>254.1582613727313</v>
@@ -2142,7 +2142,7 @@
         <v>243.3734759809475</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>197.2818334606677</v>
       </c>
       <c r="Y20" t="n">
         <v>116.3174326828064</v>
@@ -2158,16 +2158,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>129.6628866797668</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
+        <v>327.0915543203627</v>
+      </c>
+      <c r="E21" t="n">
         <v>328</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>202.6112915517259</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
         <v>8.658482198645913</v>
       </c>
       <c r="U21" t="n">
-        <v>328</v>
+        <v>5.182623911130122</v>
       </c>
       <c r="V21" t="n">
         <v>19.51066719152016</v>
@@ -2334,7 +2334,7 @@
         <v>7.940171266341508</v>
       </c>
       <c r="I23" t="n">
-        <v>1.362235606519822</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>191.2263756984131</v>
       </c>
       <c r="U23" t="n">
-        <v>257.1582613727313</v>
+        <v>258.520496979251</v>
       </c>
       <c r="V23" t="n">
         <v>237.8510241668239</v>
@@ -2395,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>274.1171222101068</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
@@ -2437,13 +2437,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>119.2643216942532</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>129.0985520093604</v>
+        <v>399.0000000000007</v>
       </c>
       <c r="S24" t="n">
-        <v>399.0000000000007</v>
+        <v>66.73324524763018</v>
       </c>
       <c r="T24" t="n">
         <v>11.65848219864591</v>
@@ -2452,13 +2452,13 @@
         <v>8.182623911130122</v>
       </c>
       <c r="V24" t="n">
-        <v>91.79858728873347</v>
+        <v>22.51066719152016</v>
       </c>
       <c r="W24" t="n">
         <v>40.37314290982852</v>
       </c>
       <c r="X24" t="n">
-        <v>399.0000000000007</v>
+        <v>27.86273944538755</v>
       </c>
       <c r="Y24" t="n">
         <v>7.391392766134345</v>
@@ -2562,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>97.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2607,19 +2607,19 @@
         <v>276.2263756984131</v>
       </c>
       <c r="U26" t="n">
-        <v>328.000000000016</v>
+        <v>294.4655996958427</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>328.0000000000123</v>
+        <v>328.0000000000118</v>
       </c>
       <c r="X26" t="n">
-        <v>72.89340367062084</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>204.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>64.00034946925459</v>
       </c>
       <c r="M28" t="n">
-        <v>121.8910945059907</v>
+        <v>158.2278736976318</v>
       </c>
       <c r="N28" t="n">
         <v>210.0987146159472</v>
@@ -2750,13 +2750,13 @@
         <v>283.4880558822936</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>328.0000000000136</v>
       </c>
       <c r="Q28" t="n">
-        <v>328</v>
+        <v>227.6628713390906</v>
       </c>
       <c r="R28" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2796,16 +2796,16 @@
         <v>103.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>97.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>97.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>92.94017126634148</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2841,22 +2841,22 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>190.7122200932833</v>
       </c>
       <c r="U29" t="n">
-        <v>328.0000000000232</v>
+        <v>328.0000000000237</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>322.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>63.77088853543078</v>
+        <v>328.0000000000191</v>
       </c>
       <c r="X29" t="n">
-        <v>285.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>204.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>212.8731952661065</v>
+        <v>212.8731952661176</v>
       </c>
       <c r="S30" t="n">
         <v>151.7332452476302</v>
@@ -2975,28 +2975,28 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>64.00034946925459</v>
       </c>
       <c r="M31" t="n">
-        <v>158.2278736976318</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>173.7619354242602</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>283.4880558822936</v>
       </c>
       <c r="P31" t="n">
-        <v>328.0000000000265</v>
+        <v>218.7755209333854</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>328.0000000000291</v>
       </c>
       <c r="R31" t="n">
-        <v>328.0000000000194</v>
+        <v>328.0000000000198</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>49.21393871924888</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -3075,13 +3075,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>11.89299192292594</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>118.2263756984131</v>
       </c>
       <c r="U32" t="n">
-        <v>184.1582613727313</v>
+        <v>107.3018580103414</v>
       </c>
       <c r="V32" t="n">
         <v>164.8510241668239</v>
@@ -3090,7 +3090,7 @@
         <v>173.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>21.5331252197772</v>
+        <v>127.2818334606677</v>
       </c>
       <c r="Y32" t="n">
         <v>46.31743268280638</v>
@@ -3103,16 +3103,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>190.000000000003</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3121,10 +3121,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>111.2534479906395</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3151,16 +3151,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>56.09855200936045</v>
+        <v>190.000000000003</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>190.000000000003</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>167.3519999999909</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -3227,10 +3227,10 @@
         <v>179.7006186397529</v>
       </c>
       <c r="Q34" t="n">
-        <v>190.0000000000507</v>
+        <v>189.8367371643153</v>
       </c>
       <c r="R34" t="n">
-        <v>189.8367371643237</v>
+        <v>190.0000000000591</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>16.99931295557451</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -3312,25 +3312,25 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>11.89299192292594</v>
       </c>
       <c r="T35" t="n">
         <v>118.2263756984131</v>
       </c>
       <c r="U35" t="n">
-        <v>126.1149908409137</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>50.90525327954412</v>
       </c>
       <c r="W35" t="n">
-        <v>129.0000000000055</v>
+        <v>129.0000000000682</v>
       </c>
       <c r="X35" t="n">
         <v>127.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>46.31743268280638</v>
       </c>
     </row>
     <row r="36">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>129.0000000000055</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3385,13 +3385,13 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>119.2643216942532</v>
       </c>
       <c r="R36" t="n">
-        <v>56.09855200936045</v>
+        <v>123.3588783057358</v>
       </c>
       <c r="S36" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>57.52464799063408</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3455,19 +3455,19 @@
         <v>0.2278736976318783</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>52.09871461594719</v>
       </c>
       <c r="O37" t="n">
         <v>125.4880558822937</v>
       </c>
       <c r="P37" t="n">
-        <v>116.9072704200744</v>
+        <v>64.80855580396154</v>
       </c>
       <c r="Q37" t="n">
-        <v>129</v>
+        <v>129.0000000000841</v>
       </c>
       <c r="R37" t="n">
-        <v>129</v>
+        <v>129.0000000000816</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>16.99931295557451</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3552,22 +3552,22 @@
         <v>11.89299192292592</v>
       </c>
       <c r="T38" t="n">
-        <v>118.2263756984131</v>
+        <v>38.41346243840577</v>
       </c>
       <c r="U38" t="n">
-        <v>129.0000000000091</v>
+        <v>129.0000000001094</v>
       </c>
       <c r="V38" t="n">
-        <v>129.0000000000091</v>
+        <v>129.0000000000845</v>
       </c>
       <c r="W38" t="n">
-        <v>112.5038323786427</v>
+        <v>129.0000000000935</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>46.31743268280638</v>
       </c>
     </row>
     <row r="39">
@@ -3583,19 +3583,19 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="H39" t="n">
-        <v>129</v>
+        <v>67.26032629636813</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>113.6232</v>
+        <v>119.2643216942532</v>
       </c>
       <c r="R39" t="n">
-        <v>129</v>
+        <v>56.09855200936042</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3695,16 +3695,16 @@
         <v>52.09871461594719</v>
       </c>
       <c r="O40" t="n">
-        <v>61.29661168642096</v>
+        <v>125.4880558822936</v>
       </c>
       <c r="P40" t="n">
-        <v>129</v>
+        <v>129.0000000001175</v>
       </c>
       <c r="Q40" t="n">
-        <v>129</v>
+        <v>129.0000000001173</v>
       </c>
       <c r="R40" t="n">
-        <v>129</v>
+        <v>64.80855580389252</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3747,58 +3747,58 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>113.6231999999508</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>129.0000000001978</v>
+      </c>
+      <c r="U41" t="n">
         <v>129.0000000000164</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>129.0000000000164</v>
       </c>
       <c r="W41" t="n">
-        <v>129.0000000000164</v>
+        <v>113.6231999997694</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3814,16 +3814,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>129.0000000001276</v>
+        <v>129.0000000001422</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>116.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>102.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>97.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>83.09646454491173</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3871,10 +3871,10 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>129.0000000001808</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>61.8546382328672</v>
+        <v>129.0000000001563</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>23.58560065647956</v>
       </c>
     </row>
     <row r="43">
@@ -3896,16 +3896,16 @@
         <v>42.11380033707866</v>
       </c>
       <c r="C43" t="n">
-        <v>27.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>40.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>35.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>29.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3923,22 +3923,22 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>126.0003494692546</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>74.68893274967522</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>129.0000000002111</v>
       </c>
       <c r="Q43" t="n">
-        <v>107.085764130181</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3959,10 +3959,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.443645430107551</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>42.46535284946236</v>
       </c>
     </row>
     <row r="44">
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>125.0000000000355</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>110.1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4023,25 +4023,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>125.0000000000355</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>125</v>
+        <v>125.0000000000355</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>110.0999999998934</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>93.59528344977946</v>
       </c>
       <c r="C45" t="n">
         <v>116.0999124455193</v>
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>97.67209722191262</v>
       </c>
       <c r="F45" t="n">
         <v>94.63624233787687</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>83.09646454491173</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4108,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4117,10 +4117,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>24.36384521660379</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6.668743836954595</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -4169,19 +4169,19 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
         <v>125</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="n">
-        <v>111.2139387192489</v>
+        <v>35.34803540566587</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4199,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>42.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.70940064975158</v>
+        <v>82.68372210732119</v>
       </c>
       <c r="C2" t="n">
         <v>32.70940064975158</v>
@@ -4330,16 +4330,16 @@
         <v>263.4206624103253</v>
       </c>
       <c r="M2" t="n">
-        <v>322.2245487608371</v>
+        <v>263.4206624103253</v>
       </c>
       <c r="N2" t="n">
-        <v>322.2245487608371</v>
+        <v>263.4206624103253</v>
       </c>
       <c r="O2" t="n">
-        <v>384.1105430081138</v>
+        <v>325.3066566576019</v>
       </c>
       <c r="P2" t="n">
-        <v>496</v>
+        <v>437.1961136494882</v>
       </c>
       <c r="Q2" t="n">
         <v>496</v>
@@ -4351,22 +4351,22 @@
         <v>418.3303111889637</v>
       </c>
       <c r="T2" t="n">
-        <v>293.0777859364384</v>
+        <v>418.3303111889637</v>
       </c>
       <c r="U2" t="n">
-        <v>293.0777859364384</v>
+        <v>418.3303111889637</v>
       </c>
       <c r="V2" t="n">
-        <v>293.0777859364384</v>
+        <v>418.3303111889637</v>
       </c>
       <c r="W2" t="n">
-        <v>293.0777859364384</v>
+        <v>403.2056873986151</v>
       </c>
       <c r="X2" t="n">
-        <v>227.9788406885202</v>
+        <v>277.9531621460898</v>
       </c>
       <c r="Y2" t="n">
-        <v>115.5369894937662</v>
+        <v>165.5113109513358</v>
       </c>
     </row>
     <row r="3">
@@ -4376,43 +4376,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="C3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="D3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="E3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="F3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="G3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="H3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="I3" t="n">
         <v>9.92</v>
       </c>
       <c r="J3" t="n">
-        <v>132.68</v>
+        <v>9.92</v>
       </c>
       <c r="K3" t="n">
-        <v>255.44</v>
+        <v>127.72</v>
       </c>
       <c r="L3" t="n">
-        <v>378.2</v>
+        <v>127.72</v>
       </c>
       <c r="M3" t="n">
-        <v>378.2</v>
+        <v>250.48</v>
       </c>
       <c r="N3" t="n">
-        <v>496</v>
+        <v>373.24</v>
       </c>
       <c r="O3" t="n">
         <v>496</v>
@@ -4430,22 +4430,22 @@
         <v>193.8827081300568</v>
       </c>
       <c r="T3" t="n">
-        <v>190.187271565768</v>
+        <v>77.5252257150165</v>
       </c>
       <c r="U3" t="n">
-        <v>190.0028029686668</v>
+        <v>77.34075711791537</v>
       </c>
       <c r="V3" t="n">
-        <v>175.3455633812727</v>
+        <v>62.68351753052128</v>
       </c>
       <c r="W3" t="n">
-        <v>142.6454190279106</v>
+        <v>29.98337317715914</v>
       </c>
       <c r="X3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="Y3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="4">
@@ -4455,22 +4455,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>233.0866383453244</v>
+        <v>9.92</v>
       </c>
       <c r="C4" t="n">
-        <v>355.8466383453244</v>
+        <v>9.92</v>
       </c>
       <c r="D4" t="n">
-        <v>469.1657824703245</v>
+        <v>9.92</v>
       </c>
       <c r="E4" t="n">
-        <v>496</v>
+        <v>127.748904211413</v>
       </c>
       <c r="F4" t="n">
-        <v>496</v>
+        <v>250.508904211413</v>
       </c>
       <c r="G4" t="n">
-        <v>496</v>
+        <v>373.268904211413</v>
       </c>
       <c r="H4" t="n">
         <v>496</v>
@@ -4500,7 +4500,7 @@
         <v>61.3266784711322</v>
       </c>
       <c r="Q4" t="n">
-        <v>61.3266784711322</v>
+        <v>9.92</v>
       </c>
       <c r="R4" t="n">
         <v>9.92</v>
@@ -4524,7 +4524,7 @@
         <v>9.92</v>
       </c>
       <c r="Y4" t="n">
-        <v>121.3293006790323</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="5">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72.24013045090724</v>
+        <v>19.26638213624294</v>
       </c>
       <c r="C5" t="n">
-        <v>22.26580899333763</v>
+        <v>19.26638213624294</v>
       </c>
       <c r="D5" t="n">
-        <v>22.26580899333763</v>
+        <v>19.26638213624294</v>
       </c>
       <c r="E5" t="n">
-        <v>17.85844575407637</v>
+        <v>14.85901889698167</v>
       </c>
       <c r="F5" t="n">
-        <v>12.9194268570947</v>
+        <v>9.92</v>
       </c>
       <c r="G5" t="n">
         <v>9.92</v>
@@ -4558,25 +4558,25 @@
         <v>9.92</v>
       </c>
       <c r="J5" t="n">
-        <v>89.36741017483399</v>
+        <v>41.43406683243596</v>
       </c>
       <c r="K5" t="n">
-        <v>188.5940057527234</v>
+        <v>140.6606624103254</v>
       </c>
       <c r="L5" t="n">
-        <v>311.3540057527234</v>
+        <v>263.4206624103253</v>
       </c>
       <c r="M5" t="n">
-        <v>311.3540057527234</v>
+        <v>263.4206624103253</v>
       </c>
       <c r="N5" t="n">
-        <v>311.3540057527234</v>
+        <v>263.4206624103253</v>
       </c>
       <c r="O5" t="n">
-        <v>373.24</v>
+        <v>325.3066566576019</v>
       </c>
       <c r="P5" t="n">
-        <v>496</v>
+        <v>437.1961136494882</v>
       </c>
       <c r="Q5" t="n">
         <v>496</v>
@@ -4591,19 +4591,19 @@
         <v>496</v>
       </c>
       <c r="U5" t="n">
-        <v>435.1870321507117</v>
+        <v>395.0239578938188</v>
       </c>
       <c r="V5" t="n">
-        <v>309.9345068981864</v>
+        <v>269.7714326412935</v>
       </c>
       <c r="W5" t="n">
-        <v>309.9345068981864</v>
+        <v>144.5189073887682</v>
       </c>
       <c r="X5" t="n">
-        <v>184.6819816456612</v>
+        <v>19.26638213624294</v>
       </c>
       <c r="Y5" t="n">
-        <v>72.24013045090724</v>
+        <v>19.26638213624294</v>
       </c>
     </row>
     <row r="6">
@@ -4613,40 +4613,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>243.0510576631284</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="C6" t="n">
-        <v>243.0510576631284</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="D6" t="n">
-        <v>117.7985324106032</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="E6" t="n">
-        <v>117.7985324106032</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="F6" t="n">
-        <v>9.92</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="G6" t="n">
-        <v>9.92</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="H6" t="n">
-        <v>9.92</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="I6" t="n">
         <v>9.92</v>
       </c>
       <c r="J6" t="n">
-        <v>127.72</v>
+        <v>132.68</v>
       </c>
       <c r="K6" t="n">
-        <v>250.48</v>
+        <v>132.68</v>
       </c>
       <c r="L6" t="n">
-        <v>373.24</v>
+        <v>132.68</v>
       </c>
       <c r="M6" t="n">
-        <v>373.24</v>
+        <v>255.44</v>
       </c>
       <c r="N6" t="n">
         <v>373.24</v>
@@ -4658,31 +4658,31 @@
         <v>496</v>
       </c>
       <c r="Q6" t="n">
-        <v>496</v>
+        <v>375.5309881876231</v>
       </c>
       <c r="R6" t="n">
-        <v>373.6782302935753</v>
+        <v>253.2092184811984</v>
       </c>
       <c r="S6" t="n">
-        <v>314.3517199424338</v>
+        <v>193.8827081300568</v>
       </c>
       <c r="T6" t="n">
-        <v>310.656283378145</v>
+        <v>190.187271565768</v>
       </c>
       <c r="U6" t="n">
-        <v>310.4718147810438</v>
+        <v>190.0028029686669</v>
       </c>
       <c r="V6" t="n">
-        <v>295.8145751936497</v>
+        <v>175.3455633812728</v>
       </c>
       <c r="W6" t="n">
-        <v>263.1144308402876</v>
+        <v>142.6454190279106</v>
       </c>
       <c r="X6" t="n">
-        <v>243.0510576631284</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="Y6" t="n">
-        <v>243.0510576631284</v>
+        <v>122.5820458507515</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>127.72</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="C7" t="n">
-        <v>127.72</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="D7" t="n">
-        <v>127.72</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="E7" t="n">
-        <v>127.72</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="F7" t="n">
-        <v>250.48</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="G7" t="n">
-        <v>250.48</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="H7" t="n">
-        <v>373.24</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="I7" t="n">
-        <v>496</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="J7" t="n">
-        <v>496</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="K7" t="n">
-        <v>496</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="L7" t="n">
         <v>496</v>
       </c>
       <c r="M7" t="n">
-        <v>496</v>
+        <v>430.113258891281</v>
       </c>
       <c r="N7" t="n">
-        <v>377.7184700849018</v>
+        <v>311.8317289761828</v>
       </c>
       <c r="O7" t="n">
-        <v>377.7184700849018</v>
+        <v>186.5792037236575</v>
       </c>
       <c r="P7" t="n">
-        <v>252.4659448323766</v>
+        <v>61.32667847113225</v>
       </c>
       <c r="Q7" t="n">
-        <v>127.2134195798513</v>
+        <v>61.32667847113225</v>
       </c>
       <c r="R7" t="n">
         <v>9.92</v>
       </c>
       <c r="S7" t="n">
-        <v>9.92</v>
+        <v>53.26820066794361</v>
       </c>
       <c r="T7" t="n">
-        <v>9.92</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="U7" t="n">
-        <v>9.92</v>
+        <v>298.7882006679436</v>
       </c>
       <c r="V7" t="n">
-        <v>9.92</v>
+        <v>421.5482006679436</v>
       </c>
       <c r="W7" t="n">
-        <v>127.72</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="X7" t="n">
-        <v>127.72</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="Y7" t="n">
-        <v>127.72</v>
+        <v>467.2903459745621</v>
       </c>
     </row>
     <row r="8">
@@ -4771,16 +4771,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.6571162169361</v>
+        <v>78.68308312901435</v>
       </c>
       <c r="C8" t="n">
-        <v>22.6571162169361</v>
+        <v>31.73906470174776</v>
       </c>
       <c r="D8" t="n">
-        <v>21.04</v>
+        <v>24.32577607563687</v>
       </c>
       <c r="E8" t="n">
-        <v>21.04</v>
+        <v>22.94871586667864</v>
       </c>
       <c r="F8" t="n">
         <v>21.04</v>
@@ -4798,22 +4798,22 @@
         <v>52.55406683243596</v>
       </c>
       <c r="K8" t="n">
-        <v>234.3851827306865</v>
+        <v>151.7806624103254</v>
       </c>
       <c r="L8" t="n">
-        <v>357.4845487608372</v>
+        <v>274.8800284404762</v>
       </c>
       <c r="M8" t="n">
-        <v>617.8545487608372</v>
+        <v>535.2500284404762</v>
       </c>
       <c r="N8" t="n">
-        <v>878.2245487608373</v>
+        <v>795.6200284404762</v>
       </c>
       <c r="O8" t="n">
-        <v>940.1105430081138</v>
+        <v>857.5060226877528</v>
       </c>
       <c r="P8" t="n">
-        <v>1052</v>
+        <v>969.3954796796389</v>
       </c>
       <c r="Q8" t="n">
         <v>1052</v>
@@ -4825,22 +4825,22 @@
         <v>1052</v>
       </c>
       <c r="T8" t="n">
-        <v>869.9531558601888</v>
+        <v>925.979122772267</v>
       </c>
       <c r="U8" t="n">
-        <v>869.9531558601888</v>
+        <v>925.979122772267</v>
       </c>
       <c r="V8" t="n">
-        <v>640.8107072068312</v>
+        <v>696.8366741189095</v>
       </c>
       <c r="W8" t="n">
-        <v>403.0597213674903</v>
+        <v>459.0856882795686</v>
       </c>
       <c r="X8" t="n">
-        <v>211.8659501950986</v>
+        <v>267.8919171071769</v>
       </c>
       <c r="Y8" t="n">
-        <v>102.4544020306477</v>
+        <v>158.480368942726</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.6965656565657</v>
+        <v>93.77692494004543</v>
       </c>
       <c r="C9" t="n">
-        <v>286.6965656565657</v>
+        <v>93.77692494004543</v>
       </c>
       <c r="D9" t="n">
-        <v>21.04</v>
+        <v>93.77692494004543</v>
       </c>
       <c r="E9" t="n">
         <v>21.04</v>
@@ -4874,19 +4874,19 @@
         <v>21.04</v>
       </c>
       <c r="J9" t="n">
-        <v>184.4287431941669</v>
+        <v>21.04</v>
       </c>
       <c r="K9" t="n">
-        <v>441.0175090998709</v>
+        <v>21.04</v>
       </c>
       <c r="L9" t="n">
-        <v>441.0175090998709</v>
+        <v>281.41</v>
       </c>
       <c r="M9" t="n">
-        <v>632.8498508427301</v>
+        <v>357.5704513002835</v>
       </c>
       <c r="N9" t="n">
-        <v>632.8498508427301</v>
+        <v>599.4014713795499</v>
       </c>
       <c r="O9" t="n">
         <v>859.7714713795499</v>
@@ -4895,31 +4895,31 @@
         <v>1052</v>
       </c>
       <c r="Q9" t="n">
-        <v>931.5309881876231</v>
+        <v>1052</v>
       </c>
       <c r="R9" t="n">
-        <v>665.8744225310575</v>
+        <v>932.7085333238783</v>
       </c>
       <c r="S9" t="n">
-        <v>400.2178568744918</v>
+        <v>667.0519676673127</v>
       </c>
       <c r="T9" t="n">
-        <v>399.5527233405061</v>
+        <v>666.3868341333269</v>
       </c>
       <c r="U9" t="n">
-        <v>399.5527233405061</v>
+        <v>666.3868341333269</v>
       </c>
       <c r="V9" t="n">
-        <v>387.925786783415</v>
+        <v>654.7598975762359</v>
       </c>
       <c r="W9" t="n">
-        <v>358.2559454603559</v>
+        <v>625.0900562531767</v>
       </c>
       <c r="X9" t="n">
-        <v>341.2228753134997</v>
+        <v>359.4334905966111</v>
       </c>
       <c r="Y9" t="n">
-        <v>341.2228753134997</v>
+        <v>359.4334905966111</v>
       </c>
     </row>
     <row r="10">
@@ -4929,49 +4929,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>514.445867574879</v>
+        <v>546.0051175531941</v>
       </c>
       <c r="C10" t="n">
-        <v>514.445867574879</v>
+        <v>674.9771233716299</v>
       </c>
       <c r="D10" t="n">
-        <v>514.445867574879</v>
+        <v>674.9771233716299</v>
       </c>
       <c r="E10" t="n">
-        <v>514.445867574879</v>
+        <v>674.9771233716299</v>
       </c>
       <c r="F10" t="n">
-        <v>641.7768401668145</v>
+        <v>674.9771233716299</v>
       </c>
       <c r="G10" t="n">
-        <v>641.7768401668145</v>
+        <v>674.9771233716299</v>
       </c>
       <c r="H10" t="n">
-        <v>817.3744272934252</v>
+        <v>674.9771233716299</v>
       </c>
       <c r="I10" t="n">
-        <v>1052</v>
+        <v>866.3329415458904</v>
       </c>
       <c r="J10" t="n">
-        <v>1052</v>
+        <v>866.3329415458904</v>
       </c>
       <c r="K10" t="n">
-        <v>1052</v>
+        <v>1020.320345974562</v>
       </c>
       <c r="L10" t="n">
         <v>1052</v>
       </c>
       <c r="M10" t="n">
-        <v>1052</v>
+        <v>989.143561921584</v>
       </c>
       <c r="N10" t="n">
-        <v>985.8770449717642</v>
+        <v>873.8923350367888</v>
       </c>
       <c r="O10" t="n">
-        <v>796.4951703431848</v>
+        <v>684.5104604082094</v>
       </c>
       <c r="P10" t="n">
-        <v>552.3531313131314</v>
+        <v>440.368421378156</v>
       </c>
       <c r="Q10" t="n">
         <v>286.6965656565657</v>
@@ -4980,25 +4980,25 @@
         <v>21.04</v>
       </c>
       <c r="S10" t="n">
-        <v>21.04</v>
+        <v>67.35820066794361</v>
       </c>
       <c r="T10" t="n">
-        <v>150.5262883559207</v>
+        <v>67.35820066794361</v>
       </c>
       <c r="U10" t="n">
-        <v>400.0665668958467</v>
+        <v>316.8984792078696</v>
       </c>
       <c r="V10" t="n">
-        <v>400.0665668958467</v>
+        <v>316.8984792078696</v>
       </c>
       <c r="W10" t="n">
-        <v>400.0665668958467</v>
+        <v>316.8984792078696</v>
       </c>
       <c r="X10" t="n">
-        <v>400.0665668958467</v>
+        <v>316.8984792078696</v>
       </c>
       <c r="Y10" t="n">
-        <v>514.445867574879</v>
+        <v>431.2777798869019</v>
       </c>
     </row>
     <row r="11">
@@ -5008,13 +5008,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>319.4984006192524</v>
+        <v>118.7888598649914</v>
       </c>
       <c r="C11" t="n">
-        <v>319.4984006192524</v>
+        <v>118.7888598649914</v>
       </c>
       <c r="D11" t="n">
-        <v>216.1255160335456</v>
+        <v>118.7888598649914</v>
       </c>
       <c r="E11" t="n">
         <v>118.7888598649914</v>
@@ -5032,19 +5032,19 @@
         <v>25.92</v>
       </c>
       <c r="J11" t="n">
-        <v>57.43406683243596</v>
+        <v>346.68</v>
       </c>
       <c r="K11" t="n">
-        <v>156.6606624103254</v>
+        <v>445.9065955778894</v>
       </c>
       <c r="L11" t="n">
-        <v>477.4206624103253</v>
+        <v>569.0059616080401</v>
       </c>
       <c r="M11" t="n">
-        <v>798.1806624103259</v>
+        <v>889.7659616080401</v>
       </c>
       <c r="N11" t="n">
-        <v>1118.940662410326</v>
+        <v>1122.224548760837</v>
       </c>
       <c r="O11" t="n">
         <v>1184.110543008114</v>
@@ -5062,22 +5062,22 @@
         <v>1296</v>
       </c>
       <c r="T11" t="n">
-        <v>1017.993559900593</v>
+        <v>1296</v>
       </c>
       <c r="U11" t="n">
-        <v>690.7208326278524</v>
+        <v>968.7272727272727</v>
       </c>
       <c r="V11" t="n">
-        <v>690.7208326278524</v>
+        <v>643.6252281143193</v>
       </c>
       <c r="W11" t="n">
-        <v>363.448105355114</v>
+        <v>316.352500841592</v>
       </c>
       <c r="X11" t="n">
-        <v>363.448105355114</v>
+        <v>118.7888598649914</v>
       </c>
       <c r="Y11" t="n">
-        <v>363.448105355114</v>
+        <v>118.7888598649914</v>
       </c>
     </row>
     <row r="12">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>224.6678327447374</v>
+        <v>224.6678327447375</v>
       </c>
       <c r="C12" t="n">
         <v>171.0315575472432</v>
@@ -5096,13 +5096,13 @@
         <v>130.6904596707759</v>
       </c>
       <c r="E12" t="n">
-        <v>95.66813924460155</v>
+        <v>95.66813924460158</v>
       </c>
       <c r="F12" t="n">
-        <v>63.71233890331179</v>
+        <v>63.71233890331181</v>
       </c>
       <c r="G12" t="n">
-        <v>46.21945913627444</v>
+        <v>46.21945913627447</v>
       </c>
       <c r="H12" t="n">
         <v>25.92</v>
@@ -5114,19 +5114,19 @@
         <v>189.3087431941669</v>
       </c>
       <c r="K12" t="n">
-        <v>349.3481095574243</v>
+        <v>189.3087431941669</v>
       </c>
       <c r="L12" t="n">
-        <v>349.3481095574243</v>
+        <v>510.0687431941669</v>
       </c>
       <c r="M12" t="n">
-        <v>541.1804513002835</v>
+        <v>701.9010849370261</v>
       </c>
       <c r="N12" t="n">
-        <v>783.0114713795499</v>
+        <v>943.7321050162925</v>
       </c>
       <c r="O12" t="n">
-        <v>1103.77147137955</v>
+        <v>1264.492105016292</v>
       </c>
       <c r="P12" t="n">
         <v>1296</v>
@@ -5156,7 +5156,7 @@
         <v>394.3122260906576</v>
       </c>
       <c r="Y12" t="n">
-        <v>301.9976879430471</v>
+        <v>301.9976879430472</v>
       </c>
     </row>
     <row r="13">
@@ -5181,13 +5181,13 @@
         <v>686.6017872557384</v>
       </c>
       <c r="G13" t="n">
-        <v>719.1971855774949</v>
+        <v>749.2782613393449</v>
       </c>
       <c r="H13" t="n">
-        <v>800.7447727041056</v>
+        <v>830.8258484659556</v>
       </c>
       <c r="I13" t="n">
-        <v>941.3203454106803</v>
+        <v>971.4014211725303</v>
       </c>
       <c r="J13" t="n">
         <v>1236.062595571328</v>
@@ -5202,16 +5202,16 @@
         <v>1073.547249326377</v>
       </c>
       <c r="N13" t="n">
-        <v>1073.547249326377</v>
+        <v>862.3364264819862</v>
       </c>
       <c r="O13" t="n">
-        <v>788.205778738202</v>
+        <v>576.9949558938108</v>
       </c>
       <c r="P13" t="n">
-        <v>680.4654545454546</v>
+        <v>249.7222286210835</v>
       </c>
       <c r="Q13" t="n">
-        <v>353.1927272727273</v>
+        <v>25.92</v>
       </c>
       <c r="R13" t="n">
         <v>25.92</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>558.8623904502231</v>
+        <v>25.92</v>
       </c>
       <c r="C14" t="n">
-        <v>415.9587760633606</v>
+        <v>25.92</v>
       </c>
       <c r="D14" t="n">
-        <v>312.5858914776537</v>
+        <v>25.92</v>
       </c>
       <c r="E14" t="n">
-        <v>312.5858914776537</v>
+        <v>25.92</v>
       </c>
       <c r="F14" t="n">
-        <v>214.7175796513791</v>
+        <v>25.92</v>
       </c>
       <c r="G14" t="n">
-        <v>118.7888598649914</v>
+        <v>25.92</v>
       </c>
       <c r="H14" t="n">
         <v>25.92</v>
@@ -5269,16 +5269,16 @@
         <v>25.92</v>
       </c>
       <c r="J14" t="n">
-        <v>57.43406683243596</v>
+        <v>346.68</v>
       </c>
       <c r="K14" t="n">
-        <v>357.6051827306854</v>
+        <v>445.9065955778894</v>
       </c>
       <c r="L14" t="n">
-        <v>480.7045487608361</v>
+        <v>569.0059616080401</v>
       </c>
       <c r="M14" t="n">
-        <v>801.4645487608367</v>
+        <v>889.7659616080401</v>
       </c>
       <c r="N14" t="n">
         <v>1122.224548760837</v>
@@ -5299,22 +5299,22 @@
         <v>1296</v>
       </c>
       <c r="T14" t="n">
-        <v>1017.993559900593</v>
+        <v>1292.720866290396</v>
       </c>
       <c r="U14" t="n">
-        <v>1017.993559900593</v>
+        <v>965.4481390176684</v>
       </c>
       <c r="V14" t="n">
-        <v>692.8915152876393</v>
+        <v>640.3460944047149</v>
       </c>
       <c r="W14" t="n">
-        <v>692.8915152876393</v>
+        <v>313.0733671319876</v>
       </c>
       <c r="X14" t="n">
-        <v>558.8623904502231</v>
+        <v>25.92</v>
       </c>
       <c r="Y14" t="n">
-        <v>558.8623904502231</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="15">
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>224.6678327447375</v>
+        <v>224.6678327447374</v>
       </c>
       <c r="C15" t="n">
         <v>171.0315575472432</v>
@@ -5333,13 +5333,13 @@
         <v>130.6904596707759</v>
       </c>
       <c r="E15" t="n">
-        <v>95.66813924460158</v>
+        <v>95.66813924460155</v>
       </c>
       <c r="F15" t="n">
-        <v>63.71233890331181</v>
+        <v>63.71233890331179</v>
       </c>
       <c r="G15" t="n">
-        <v>46.21945913627447</v>
+        <v>46.21945913627444</v>
       </c>
       <c r="H15" t="n">
         <v>25.92</v>
@@ -5354,13 +5354,13 @@
         <v>445.897509099871</v>
       </c>
       <c r="L15" t="n">
-        <v>445.897509099871</v>
+        <v>670.1081095574243</v>
       </c>
       <c r="M15" t="n">
-        <v>637.7298508427302</v>
+        <v>861.9404513002835</v>
       </c>
       <c r="N15" t="n">
-        <v>879.5608709219966</v>
+        <v>1103.77147137955</v>
       </c>
       <c r="O15" t="n">
         <v>1103.77147137955</v>
@@ -5372,19 +5372,19 @@
         <v>1296</v>
       </c>
       <c r="R15" t="n">
-        <v>1082.515156296862</v>
+        <v>1080.748937364282</v>
       </c>
       <c r="S15" t="n">
-        <v>930.2593530164277</v>
+        <v>928.493134083848</v>
       </c>
       <c r="T15" t="n">
-        <v>833.6346235228459</v>
+        <v>831.8684045902662</v>
       </c>
       <c r="U15" t="n">
-        <v>740.5208619964518</v>
+        <v>738.7546430638721</v>
       </c>
       <c r="V15" t="n">
-        <v>632.9343294797648</v>
+        <v>631.1681105471851</v>
       </c>
       <c r="W15" t="n">
         <v>507.3048921971097</v>
@@ -5393,7 +5393,7 @@
         <v>394.3122260906576</v>
       </c>
       <c r="Y15" t="n">
-        <v>301.9976879430472</v>
+        <v>301.9976879430471</v>
       </c>
     </row>
     <row r="16">
@@ -5403,28 +5403,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>539.3296847471041</v>
+        <v>569.4107605089541</v>
       </c>
       <c r="C16" t="n">
-        <v>574.2516905655399</v>
+        <v>604.3327663273899</v>
       </c>
       <c r="D16" t="n">
-        <v>596.4908346905399</v>
+        <v>626.5719104523899</v>
       </c>
       <c r="E16" t="n">
-        <v>623.2397389019529</v>
+        <v>653.3208146638029</v>
       </c>
       <c r="F16" t="n">
-        <v>656.5207114938884</v>
+        <v>686.6017872557384</v>
       </c>
       <c r="G16" t="n">
-        <v>719.1971855774949</v>
+        <v>749.2782613393449</v>
       </c>
       <c r="H16" t="n">
-        <v>800.7447727041056</v>
+        <v>830.8258484659556</v>
       </c>
       <c r="I16" t="n">
-        <v>941.3203454106803</v>
+        <v>971.4014211725303</v>
       </c>
       <c r="J16" t="n">
         <v>1236.062595571328</v>
@@ -5448,7 +5448,7 @@
         <v>249.7222286210835</v>
       </c>
       <c r="Q16" t="n">
-        <v>249.7222286210835</v>
+        <v>25.92</v>
       </c>
       <c r="R16" t="n">
         <v>25.92</v>
@@ -5460,19 +5460,19 @@
         <v>124.4107414538868</v>
       </c>
       <c r="U16" t="n">
-        <v>249.8199442319628</v>
+        <v>279.9010199938128</v>
       </c>
       <c r="V16" t="n">
-        <v>357.5613371179088</v>
+        <v>387.6424128797588</v>
       </c>
       <c r="W16" t="n">
-        <v>438.3722553775862</v>
+        <v>468.4533311394362</v>
       </c>
       <c r="X16" t="n">
-        <v>498.3230464017797</v>
+        <v>528.4041221636297</v>
       </c>
       <c r="Y16" t="n">
-        <v>518.652347080812</v>
+        <v>548.733422842662</v>
       </c>
     </row>
     <row r="17">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>128.92631934605</v>
+        <v>58.40739613105635</v>
       </c>
       <c r="C17" t="n">
-        <v>73.90149283797533</v>
+        <v>58.40739613105635</v>
       </c>
       <c r="D17" t="n">
         <v>58.40739613105635</v>
@@ -5506,16 +5506,16 @@
         <v>25.92</v>
       </c>
       <c r="J17" t="n">
-        <v>258.3785871527959</v>
+        <v>346.68</v>
       </c>
       <c r="K17" t="n">
-        <v>357.6051827306854</v>
+        <v>445.9065955778894</v>
       </c>
       <c r="L17" t="n">
-        <v>480.7045487608361</v>
+        <v>569.0059616080401</v>
       </c>
       <c r="M17" t="n">
-        <v>801.4645487608367</v>
+        <v>889.7659616080401</v>
       </c>
       <c r="N17" t="n">
         <v>1122.224548760837</v>
@@ -5539,19 +5539,19 @@
         <v>1023.152153917839</v>
       </c>
       <c r="U17" t="n">
-        <v>817.3518201401433</v>
+        <v>766.426637379727</v>
       </c>
       <c r="V17" t="n">
-        <v>580.1285634059777</v>
+        <v>529.2033806455614</v>
       </c>
       <c r="W17" t="n">
-        <v>334.2967694858287</v>
+        <v>283.3715867254124</v>
       </c>
       <c r="X17" t="n">
-        <v>334.2967694858287</v>
+        <v>84.09700747221265</v>
       </c>
       <c r="Y17" t="n">
-        <v>216.8044132405697</v>
+        <v>58.40739613105635</v>
       </c>
     </row>
     <row r="18">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.92</v>
+        <v>557.8505975269959</v>
       </c>
       <c r="C18" t="n">
-        <v>25.92</v>
+        <v>557.8505975269959</v>
       </c>
       <c r="D18" t="n">
-        <v>25.92</v>
+        <v>557.8505975269959</v>
       </c>
       <c r="E18" t="n">
-        <v>25.92</v>
+        <v>230.5778702542686</v>
       </c>
       <c r="F18" t="n">
-        <v>25.92</v>
+        <v>230.5778702542686</v>
       </c>
       <c r="G18" t="n">
-        <v>25.92</v>
+        <v>230.5778702542686</v>
       </c>
       <c r="H18" t="n">
-        <v>25.92</v>
+        <v>230.5778702542686</v>
       </c>
       <c r="I18" t="n">
         <v>25.92</v>
@@ -5588,19 +5588,19 @@
         <v>189.3087431941669</v>
       </c>
       <c r="K18" t="n">
-        <v>445.897509099871</v>
+        <v>189.3087431941669</v>
       </c>
       <c r="L18" t="n">
-        <v>445.897509099871</v>
+        <v>510.0687431941669</v>
       </c>
       <c r="M18" t="n">
-        <v>541.1804513002835</v>
+        <v>701.9010849370261</v>
       </c>
       <c r="N18" t="n">
-        <v>783.0114713795499</v>
+        <v>943.7321050162925</v>
       </c>
       <c r="O18" t="n">
-        <v>1103.77147137955</v>
+        <v>1264.492105016292</v>
       </c>
       <c r="P18" t="n">
         <v>1296</v>
@@ -5615,22 +5615,22 @@
         <v>1104.250709841423</v>
       </c>
       <c r="T18" t="n">
-        <v>776.9779825686962</v>
+        <v>1095.50476822663</v>
       </c>
       <c r="U18" t="n">
-        <v>449.7052552959689</v>
+        <v>952.423602700077</v>
       </c>
       <c r="V18" t="n">
-        <v>429.9975106580698</v>
+        <v>625.1508754273498</v>
       </c>
       <c r="W18" t="n">
-        <v>102.7247833853424</v>
+        <v>587.4002260234826</v>
       </c>
       <c r="X18" t="n">
-        <v>30.35575026882257</v>
+        <v>562.2863477958184</v>
       </c>
       <c r="Y18" t="n">
-        <v>25.92</v>
+        <v>557.8505975269959</v>
       </c>
     </row>
     <row r="19">
@@ -5640,28 +5640,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>639.2724028488492</v>
+        <v>957.8308324864121</v>
       </c>
       <c r="C19" t="n">
-        <v>760.324408667285</v>
+        <v>957.8308324864121</v>
       </c>
       <c r="D19" t="n">
-        <v>760.324408667285</v>
+        <v>957.8308324864121</v>
       </c>
       <c r="E19" t="n">
-        <v>760.324408667285</v>
+        <v>957.8308324864121</v>
       </c>
       <c r="F19" t="n">
-        <v>760.324408667285</v>
+        <v>957.8308324864121</v>
       </c>
       <c r="G19" t="n">
-        <v>874.9171777258252</v>
+        <v>957.8308324864121</v>
       </c>
       <c r="H19" t="n">
-        <v>1042.594764852436</v>
+        <v>957.8308324864121</v>
       </c>
       <c r="I19" t="n">
-        <v>1269.300337559011</v>
+        <v>957.8308324864121</v>
       </c>
       <c r="J19" t="n">
         <v>1269.300337559011</v>
@@ -5691,25 +5691,25 @@
         <v>25.92</v>
       </c>
       <c r="S19" t="n">
-        <v>25.92</v>
+        <v>64.31820066794363</v>
       </c>
       <c r="T19" t="n">
-        <v>25.92</v>
+        <v>248.9389421218305</v>
       </c>
       <c r="U19" t="n">
-        <v>25.92</v>
+        <v>490.5592206617564</v>
       </c>
       <c r="V19" t="n">
-        <v>219.791392885946</v>
+        <v>684.4306135477024</v>
       </c>
       <c r="W19" t="n">
-        <v>386.7323111456234</v>
+        <v>851.3715318073798</v>
       </c>
       <c r="X19" t="n">
-        <v>532.8131021698169</v>
+        <v>851.3715318073798</v>
       </c>
       <c r="Y19" t="n">
-        <v>639.2724028488492</v>
+        <v>957.8308324864121</v>
       </c>
     </row>
     <row r="20">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94.00113658563347</v>
+        <v>116.2063154522467</v>
       </c>
       <c r="C20" t="n">
-        <v>74.22149283797533</v>
+        <v>61.18148894417202</v>
       </c>
       <c r="D20" t="n">
-        <v>58.72739613105635</v>
+        <v>45.68739223725304</v>
       </c>
       <c r="E20" t="n">
-        <v>49.26952784129004</v>
+        <v>36.22952394748673</v>
       </c>
       <c r="F20" t="n">
-        <v>39.28000389380332</v>
+        <v>26.24</v>
       </c>
       <c r="G20" t="n">
-        <v>31.23007198620355</v>
+        <v>26.24</v>
       </c>
       <c r="H20" t="n">
         <v>26.24</v>
@@ -5743,25 +5743,25 @@
         <v>26.24</v>
       </c>
       <c r="J20" t="n">
-        <v>350.9600000000005</v>
+        <v>57.75406683243596</v>
       </c>
       <c r="K20" t="n">
-        <v>450.18659557789</v>
+        <v>156.9806624103254</v>
       </c>
       <c r="L20" t="n">
-        <v>573.2859616080407</v>
+        <v>280.0800284404762</v>
       </c>
       <c r="M20" t="n">
-        <v>573.2859616080408</v>
+        <v>604.8000284404766</v>
       </c>
       <c r="N20" t="n">
-        <v>898.0059616080413</v>
+        <v>929.5200284404771</v>
       </c>
       <c r="O20" t="n">
-        <v>1200.110543008114</v>
+        <v>991.4060226877536</v>
       </c>
       <c r="P20" t="n">
-        <v>1312</v>
+        <v>1103.29547967964</v>
       </c>
       <c r="Q20" t="n">
         <v>1312</v>
@@ -5773,22 +5773,22 @@
         <v>1229.279806138459</v>
       </c>
       <c r="T20" t="n">
-        <v>1039.152153917839</v>
+        <v>1172.753818143133</v>
       </c>
       <c r="U20" t="n">
-        <v>782.4266373797268</v>
+        <v>916.02830160502</v>
       </c>
       <c r="V20" t="n">
-        <v>545.2033806455612</v>
+        <v>678.8050448708544</v>
       </c>
       <c r="W20" t="n">
-        <v>299.3715867254122</v>
+        <v>432.9732509507054</v>
       </c>
       <c r="X20" t="n">
-        <v>299.3715867254122</v>
+        <v>233.6986716975057</v>
       </c>
       <c r="Y20" t="n">
-        <v>181.8792304801532</v>
+        <v>116.2063154522467</v>
       </c>
     </row>
     <row r="21">
@@ -5798,43 +5798,43 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>693.1836143752453</v>
+        <v>1019.261772040771</v>
       </c>
       <c r="C21" t="n">
-        <v>562.2110015674</v>
+        <v>1019.261772040771</v>
       </c>
       <c r="D21" t="n">
-        <v>230.8978702542686</v>
+        <v>688.8662626262627</v>
       </c>
       <c r="E21" t="n">
-        <v>230.8978702542686</v>
+        <v>357.5531313131314</v>
       </c>
       <c r="F21" t="n">
-        <v>230.8978702542686</v>
+        <v>26.24</v>
       </c>
       <c r="G21" t="n">
-        <v>230.8978702542686</v>
+        <v>26.24</v>
       </c>
       <c r="H21" t="n">
-        <v>230.8978702542686</v>
+        <v>26.24</v>
       </c>
       <c r="I21" t="n">
         <v>26.24</v>
       </c>
       <c r="J21" t="n">
-        <v>26.24</v>
+        <v>189.6287431941669</v>
       </c>
       <c r="K21" t="n">
-        <v>282.8287659057041</v>
+        <v>446.217509099871</v>
       </c>
       <c r="L21" t="n">
-        <v>603.2191296366907</v>
+        <v>446.217509099871</v>
       </c>
       <c r="M21" t="n">
-        <v>795.0514713795499</v>
+        <v>638.0498508427302</v>
       </c>
       <c r="N21" t="n">
-        <v>795.0514713795499</v>
+        <v>879.8808709219966</v>
       </c>
       <c r="O21" t="n">
         <v>1119.77147137955</v>
@@ -5855,19 +5855,19 @@
         <v>1111.50476822663</v>
       </c>
       <c r="U21" t="n">
-        <v>780.1916369134983</v>
+        <v>1106.269794579023</v>
       </c>
       <c r="V21" t="n">
-        <v>760.4838922755991</v>
+        <v>1086.562049941124</v>
       </c>
       <c r="W21" t="n">
-        <v>722.7332428717319</v>
+        <v>1048.811400537257</v>
       </c>
       <c r="X21" t="n">
-        <v>697.6193646440678</v>
+        <v>1023.697522309593</v>
       </c>
       <c r="Y21" t="n">
-        <v>693.1836143752453</v>
+        <v>1019.261772040771</v>
       </c>
     </row>
     <row r="22">
@@ -5877,22 +5877,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>794.1486261691213</v>
+        <v>658.5338533408921</v>
       </c>
       <c r="C22" t="n">
-        <v>794.1486261691213</v>
+        <v>779.5858591593278</v>
       </c>
       <c r="D22" t="n">
-        <v>804.9890405828544</v>
+        <v>779.5858591593278</v>
       </c>
       <c r="E22" t="n">
-        <v>917.8679447942674</v>
+        <v>779.5858591593278</v>
       </c>
       <c r="F22" t="n">
-        <v>917.8679447942674</v>
+        <v>898.9968317512632</v>
       </c>
       <c r="G22" t="n">
-        <v>1066.674418877874</v>
+        <v>898.9968317512632</v>
       </c>
       <c r="H22" t="n">
         <v>1066.674418877874</v>
@@ -5934,19 +5934,19 @@
         <v>26.24</v>
       </c>
       <c r="U22" t="n">
-        <v>267.860278539926</v>
+        <v>26.24</v>
       </c>
       <c r="V22" t="n">
-        <v>267.860278539926</v>
+        <v>132.2455057116967</v>
       </c>
       <c r="W22" t="n">
-        <v>434.8011967996034</v>
+        <v>299.1864239713741</v>
       </c>
       <c r="X22" t="n">
-        <v>580.8819878237969</v>
+        <v>445.2672149955677</v>
       </c>
       <c r="Y22" t="n">
-        <v>687.3412885028291</v>
+        <v>551.7265156745999</v>
       </c>
     </row>
     <row r="23">
@@ -5956,25 +5956,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>154.4841330900094</v>
+        <v>153.1081375278682</v>
       </c>
       <c r="C23" t="n">
-        <v>96.42900355163172</v>
+        <v>95.05300798949048</v>
       </c>
       <c r="D23" t="n">
-        <v>77.90460381440971</v>
+        <v>76.52860825226847</v>
       </c>
       <c r="E23" t="n">
-        <v>65.41643249434037</v>
+        <v>64.04043693219913</v>
       </c>
       <c r="F23" t="n">
-        <v>52.39660551655061</v>
+        <v>51.02060995440938</v>
       </c>
       <c r="G23" t="n">
-        <v>41.31637057864781</v>
+        <v>39.94037501650658</v>
       </c>
       <c r="H23" t="n">
-        <v>33.29599556214124</v>
+        <v>31.92</v>
       </c>
       <c r="I23" t="n">
         <v>31.92</v>
@@ -5983,19 +5983,19 @@
         <v>426.9300000000007</v>
       </c>
       <c r="K23" t="n">
-        <v>526.1565955778901</v>
+        <v>821.9400000000006</v>
       </c>
       <c r="L23" t="n">
-        <v>744.0940057527221</v>
+        <v>945.0393660301514</v>
       </c>
       <c r="M23" t="n">
-        <v>744.0940057527221</v>
+        <v>945.0393660301514</v>
       </c>
       <c r="N23" t="n">
-        <v>744.0940057527221</v>
+        <v>1027.214548760837</v>
       </c>
       <c r="O23" t="n">
-        <v>805.9799999999987</v>
+        <v>1089.100543008113</v>
       </c>
       <c r="P23" t="n">
         <v>1200.989999999999</v>
@@ -6013,19 +6013,19 @@
         <v>1317.091547857233</v>
       </c>
       <c r="U23" t="n">
-        <v>1057.335728288818</v>
+        <v>1055.959732726677</v>
       </c>
       <c r="V23" t="n">
-        <v>817.082168524349</v>
+        <v>815.7061729622078</v>
       </c>
       <c r="W23" t="n">
-        <v>568.2200715738969</v>
+        <v>566.8440760117558</v>
       </c>
       <c r="X23" t="n">
-        <v>365.9151892903942</v>
+        <v>364.5391937282529</v>
       </c>
       <c r="Y23" t="n">
-        <v>245.3925300148321</v>
+        <v>244.0165344526909</v>
       </c>
     </row>
     <row r="24">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>378.0534315372855</v>
+        <v>1006.391622555275</v>
       </c>
       <c r="C24" t="n">
-        <v>378.0534315372855</v>
+        <v>729.505640524864</v>
       </c>
       <c r="D24" t="n">
         <v>378.0534315372855</v>
@@ -6059,13 +6059,13 @@
         <v>31.92</v>
       </c>
       <c r="J24" t="n">
-        <v>31.92</v>
+        <v>195.3087431941669</v>
       </c>
       <c r="K24" t="n">
-        <v>269.7903087313354</v>
+        <v>451.897509099871</v>
       </c>
       <c r="L24" t="n">
-        <v>631.7629420246487</v>
+        <v>813.8701423931843</v>
       </c>
       <c r="M24" t="n">
         <v>823.5952837675079</v>
@@ -6080,31 +6080,31 @@
         <v>1596</v>
       </c>
       <c r="Q24" t="n">
-        <v>1475.530988187623</v>
+        <v>1596</v>
       </c>
       <c r="R24" t="n">
-        <v>1345.12841040039</v>
+        <v>1192.969696969696</v>
       </c>
       <c r="S24" t="n">
-        <v>942.0981073700866</v>
+        <v>1125.562378537747</v>
       </c>
       <c r="T24" t="n">
-        <v>930.3218627249897</v>
+        <v>1113.78613389265</v>
       </c>
       <c r="U24" t="n">
-        <v>922.0565860470805</v>
+        <v>1105.52085721474</v>
       </c>
       <c r="V24" t="n">
-        <v>829.3307403008851</v>
+        <v>1082.782809546538</v>
       </c>
       <c r="W24" t="n">
-        <v>788.5497878667148</v>
+        <v>1042.001857112368</v>
       </c>
       <c r="X24" t="n">
-        <v>385.5194848364111</v>
+        <v>1013.857675854401</v>
       </c>
       <c r="Y24" t="n">
-        <v>378.0534315372855</v>
+        <v>1006.391622555275</v>
       </c>
     </row>
     <row r="25">
@@ -6114,31 +6114,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>261.9625212601552</v>
+        <v>888.6157427376137</v>
       </c>
       <c r="C25" t="n">
-        <v>261.9625212601552</v>
+        <v>1006.697748556049</v>
       </c>
       <c r="D25" t="n">
-        <v>261.9625212601552</v>
+        <v>1006.697748556049</v>
       </c>
       <c r="E25" t="n">
-        <v>261.9625212601552</v>
+        <v>1006.697748556049</v>
       </c>
       <c r="F25" t="n">
-        <v>261.9625212601552</v>
+        <v>1006.697748556049</v>
       </c>
       <c r="G25" t="n">
-        <v>407.7989953437618</v>
+        <v>1152.534222639656</v>
       </c>
       <c r="H25" t="n">
-        <v>572.5065824703725</v>
+        <v>1317.241809766267</v>
       </c>
       <c r="I25" t="n">
-        <v>796.2421551769471</v>
+        <v>1317.241809766267</v>
       </c>
       <c r="J25" t="n">
-        <v>1174.144405337595</v>
+        <v>1317.241809766267</v>
       </c>
       <c r="K25" t="n">
         <v>1317.241809766267</v>
@@ -6171,19 +6171,19 @@
         <v>31.92</v>
       </c>
       <c r="U25" t="n">
-        <v>31.92</v>
+        <v>183.3060022224724</v>
       </c>
       <c r="V25" t="n">
-        <v>31.92</v>
+        <v>374.2073951084184</v>
       </c>
       <c r="W25" t="n">
-        <v>31.92</v>
+        <v>538.1783133680958</v>
       </c>
       <c r="X25" t="n">
-        <v>175.0307910241935</v>
+        <v>681.2891043922893</v>
       </c>
       <c r="Y25" t="n">
-        <v>261.9625212601552</v>
+        <v>784.7784050713216</v>
       </c>
     </row>
     <row r="26">
@@ -6193,16 +6193,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>125.1184128363756</v>
+        <v>26.24</v>
       </c>
       <c r="C26" t="n">
-        <v>125.1184128363756</v>
+        <v>26.24</v>
       </c>
       <c r="D26" t="n">
-        <v>125.1184128363756</v>
+        <v>26.24</v>
       </c>
       <c r="E26" t="n">
-        <v>125.1184128363756</v>
+        <v>26.24</v>
       </c>
       <c r="F26" t="n">
         <v>26.24</v>
@@ -6217,25 +6217,25 @@
         <v>26.24</v>
       </c>
       <c r="J26" t="n">
-        <v>350.96</v>
+        <v>57.75406683243596</v>
       </c>
       <c r="K26" t="n">
-        <v>450.1865955778895</v>
+        <v>156.9806624103254</v>
       </c>
       <c r="L26" t="n">
-        <v>774.9065955778894</v>
+        <v>280.0800284404762</v>
       </c>
       <c r="M26" t="n">
-        <v>1099.626595577889</v>
+        <v>604.8000284404761</v>
       </c>
       <c r="N26" t="n">
-        <v>1099.626595577889</v>
+        <v>929.5200284404762</v>
       </c>
       <c r="O26" t="n">
-        <v>1161.512589825166</v>
+        <v>991.4060226877527</v>
       </c>
       <c r="P26" t="n">
-        <v>1273.402046817052</v>
+        <v>1103.295479679639</v>
       </c>
       <c r="Q26" t="n">
         <v>1312</v>
@@ -6250,19 +6250,19 @@
         <v>861.3743761400617</v>
       </c>
       <c r="U26" t="n">
-        <v>530.0612448269142</v>
+        <v>563.9343764472912</v>
       </c>
       <c r="V26" t="n">
-        <v>530.0612448269142</v>
+        <v>563.9343764472912</v>
       </c>
       <c r="W26" t="n">
-        <v>198.7481135137704</v>
+        <v>232.6212451341479</v>
       </c>
       <c r="X26" t="n">
-        <v>125.1184128363756</v>
+        <v>232.6212451341479</v>
       </c>
       <c r="Y26" t="n">
-        <v>125.1184128363756</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="27">
@@ -6296,22 +6296,22 @@
         <v>26.24</v>
       </c>
       <c r="J27" t="n">
-        <v>26.24</v>
+        <v>189.6287431941669</v>
       </c>
       <c r="K27" t="n">
-        <v>228.8966381778744</v>
+        <v>361.3881095574243</v>
       </c>
       <c r="L27" t="n">
-        <v>553.6166381778744</v>
+        <v>686.1081095574243</v>
       </c>
       <c r="M27" t="n">
-        <v>745.4489799207336</v>
+        <v>877.9404513002835</v>
       </c>
       <c r="N27" t="n">
-        <v>987.28</v>
+        <v>1119.77147137955</v>
       </c>
       <c r="O27" t="n">
-        <v>1312</v>
+        <v>1119.77147137955</v>
       </c>
       <c r="P27" t="n">
         <v>1312</v>
@@ -6381,22 +6381,22 @@
         <v>1310.56107576185</v>
       </c>
       <c r="L28" t="n">
-        <v>1310.56107576185</v>
+        <v>1245.914258116138</v>
       </c>
       <c r="M28" t="n">
-        <v>1187.438758079031</v>
+        <v>1086.088123068025</v>
       </c>
       <c r="N28" t="n">
-        <v>975.217834224539</v>
+        <v>873.8671992135332</v>
       </c>
       <c r="O28" t="n">
-        <v>688.8662626262627</v>
+        <v>587.5156276152568</v>
       </c>
       <c r="P28" t="n">
-        <v>688.8662626262627</v>
+        <v>256.2024963021117</v>
       </c>
       <c r="Q28" t="n">
-        <v>357.5531313131314</v>
+        <v>26.24</v>
       </c>
       <c r="R28" t="n">
         <v>26.24</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>421.7271164859311</v>
+        <v>130.6229855958079</v>
       </c>
       <c r="C29" t="n">
-        <v>421.7271164859311</v>
+        <v>130.6229855958079</v>
       </c>
       <c r="D29" t="n">
-        <v>317.3441308901232</v>
+        <v>26.24</v>
       </c>
       <c r="E29" t="n">
-        <v>218.997373711468</v>
+        <v>26.24</v>
       </c>
       <c r="F29" t="n">
-        <v>120.1189608750924</v>
+        <v>26.24</v>
       </c>
       <c r="G29" t="n">
-        <v>120.1189608750924</v>
+        <v>26.24</v>
       </c>
       <c r="H29" t="n">
         <v>26.24</v>
@@ -6454,25 +6454,25 @@
         <v>26.24</v>
       </c>
       <c r="J29" t="n">
-        <v>350.9600000000009</v>
+        <v>57.75406683243596</v>
       </c>
       <c r="K29" t="n">
-        <v>675.680000000001</v>
+        <v>156.9806624103254</v>
       </c>
       <c r="L29" t="n">
-        <v>798.7793660301517</v>
+        <v>280.0800284404762</v>
       </c>
       <c r="M29" t="n">
-        <v>925.3940057527225</v>
+        <v>604.800028440477</v>
       </c>
       <c r="N29" t="n">
-        <v>925.3940057527225</v>
+        <v>929.520028440478</v>
       </c>
       <c r="O29" t="n">
-        <v>987.2799999999991</v>
+        <v>991.4060226877546</v>
       </c>
       <c r="P29" t="n">
-        <v>1312</v>
+        <v>1103.295479679641</v>
       </c>
       <c r="Q29" t="n">
         <v>1312</v>
@@ -6484,22 +6484,22 @@
         <v>1312</v>
       </c>
       <c r="T29" t="n">
-        <v>1312</v>
+        <v>1119.361393845168</v>
       </c>
       <c r="U29" t="n">
-        <v>980.6868686868452</v>
+        <v>788.048262532013</v>
       </c>
       <c r="V29" t="n">
-        <v>980.6868686868452</v>
+        <v>461.9361169089585</v>
       </c>
       <c r="W29" t="n">
-        <v>916.2718297621676</v>
+        <v>130.6229855958079</v>
       </c>
       <c r="X29" t="n">
-        <v>628.108361620079</v>
+        <v>130.6229855958079</v>
       </c>
       <c r="Y29" t="n">
-        <v>421.7271164859311</v>
+        <v>130.6229855958079</v>
       </c>
     </row>
     <row r="30">
@@ -6539,13 +6539,13 @@
         <v>446.217509099871</v>
       </c>
       <c r="L30" t="n">
-        <v>770.937509099871</v>
+        <v>446.217509099871</v>
       </c>
       <c r="M30" t="n">
-        <v>795.0514713795499</v>
+        <v>553.2204513002825</v>
       </c>
       <c r="N30" t="n">
-        <v>795.0514713795499</v>
+        <v>795.051471379549</v>
       </c>
       <c r="O30" t="n">
         <v>1119.77147137955</v>
@@ -6554,7 +6554,7 @@
         <v>1312</v>
       </c>
       <c r="Q30" t="n">
-        <v>1312</v>
+        <v>1312.000000000011</v>
       </c>
       <c r="R30" t="n">
         <v>1096.976570438276</v>
@@ -6618,25 +6618,25 @@
         <v>1310.56107576185</v>
       </c>
       <c r="L31" t="n">
-        <v>1310.56107576185</v>
+        <v>1245.914258116138</v>
       </c>
       <c r="M31" t="n">
-        <v>1150.734940713737</v>
+        <v>1245.914258116138</v>
       </c>
       <c r="N31" t="n">
-        <v>975.2178342245854</v>
+        <v>1245.914258116138</v>
       </c>
       <c r="O31" t="n">
-        <v>688.866262626309</v>
+        <v>959.5626865178619</v>
       </c>
       <c r="P31" t="n">
-        <v>357.5531313131509</v>
+        <v>738.5773118376746</v>
       </c>
       <c r="Q31" t="n">
-        <v>357.5531313131509</v>
+        <v>407.2641805245139</v>
       </c>
       <c r="R31" t="n">
-        <v>26.24</v>
+        <v>75.95104921136252</v>
       </c>
       <c r="S31" t="n">
         <v>26.24</v>
@@ -6706,10 +6706,10 @@
         <v>457.1400284404792</v>
       </c>
       <c r="O32" t="n">
-        <v>645.2400284404822</v>
+        <v>519.0260226877558</v>
       </c>
       <c r="P32" t="n">
-        <v>760</v>
+        <v>630.915479679642</v>
       </c>
       <c r="Q32" t="n">
         <v>760</v>
@@ -6718,25 +6718,25 @@
         <v>760</v>
       </c>
       <c r="S32" t="n">
-        <v>747.9868768455293</v>
+        <v>760</v>
       </c>
       <c r="T32" t="n">
-        <v>628.5662953319807</v>
+        <v>640.5794184864515</v>
       </c>
       <c r="U32" t="n">
-        <v>442.5478495009389</v>
+        <v>532.1937033244905</v>
       </c>
       <c r="V32" t="n">
-        <v>276.0316634738441</v>
+        <v>365.6775172973956</v>
       </c>
       <c r="W32" t="n">
-        <v>100.9069402607658</v>
+        <v>190.5527940843173</v>
       </c>
       <c r="X32" t="n">
-        <v>79.15630872563727</v>
+        <v>61.98528553818827</v>
       </c>
       <c r="Y32" t="n">
-        <v>32.371023187449</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="33">
@@ -6746,25 +6746,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>511.415604030949</v>
+        <v>207.119191919195</v>
       </c>
       <c r="C33" t="n">
-        <v>511.415604030949</v>
+        <v>207.119191919195</v>
       </c>
       <c r="D33" t="n">
-        <v>319.4964121117571</v>
+        <v>207.119191919195</v>
       </c>
       <c r="E33" t="n">
-        <v>319.4964121117571</v>
+        <v>15.2</v>
       </c>
       <c r="F33" t="n">
-        <v>319.4964121117571</v>
+        <v>15.2</v>
       </c>
       <c r="G33" t="n">
-        <v>319.4964121117571</v>
+        <v>15.2</v>
       </c>
       <c r="H33" t="n">
-        <v>127.5772201925651</v>
+        <v>15.2</v>
       </c>
       <c r="I33" t="n">
         <v>15.2</v>
@@ -6773,19 +6773,19 @@
         <v>178.5887431941669</v>
       </c>
       <c r="K33" t="n">
-        <v>178.5887431941669</v>
+        <v>366.6887431941699</v>
       </c>
       <c r="L33" t="n">
-        <v>178.5887431941669</v>
+        <v>554.7887431941729</v>
       </c>
       <c r="M33" t="n">
-        <v>366.6887431941668</v>
+        <v>571.899999999997</v>
       </c>
       <c r="N33" t="n">
-        <v>554.7887431941668</v>
+        <v>571.899999999997</v>
       </c>
       <c r="O33" t="n">
-        <v>742.8887431941669</v>
+        <v>571.899999999997</v>
       </c>
       <c r="P33" t="n">
         <v>760</v>
@@ -6794,28 +6794,28 @@
         <v>760</v>
       </c>
       <c r="R33" t="n">
-        <v>703.3347959501409</v>
+        <v>568.080808080805</v>
       </c>
       <c r="S33" t="n">
-        <v>703.3347959501409</v>
+        <v>376.16161616161</v>
       </c>
       <c r="T33" t="n">
-        <v>703.3347959501409</v>
+        <v>376.16161616161</v>
       </c>
       <c r="U33" t="n">
-        <v>703.3347959501409</v>
+        <v>207.119191919195</v>
       </c>
       <c r="V33" t="n">
-        <v>703.3347959501409</v>
+        <v>207.119191919195</v>
       </c>
       <c r="W33" t="n">
-        <v>703.3347959501409</v>
+        <v>207.119191919195</v>
       </c>
       <c r="X33" t="n">
-        <v>703.3347959501409</v>
+        <v>207.119191919195</v>
       </c>
       <c r="Y33" t="n">
-        <v>703.3347959501409</v>
+        <v>207.119191919195</v>
       </c>
     </row>
     <row r="34">
@@ -6825,19 +6825,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>567.1593006790322</v>
+        <v>203.300000000003</v>
       </c>
       <c r="C34" t="n">
-        <v>567.1593006790322</v>
+        <v>203.300000000003</v>
       </c>
       <c r="D34" t="n">
-        <v>567.1593006790322</v>
+        <v>203.300000000003</v>
       </c>
       <c r="E34" t="n">
-        <v>571.9</v>
+        <v>385.478904211416</v>
       </c>
       <c r="F34" t="n">
-        <v>571.9</v>
+        <v>571.899999999997</v>
       </c>
       <c r="G34" t="n">
         <v>760</v>
@@ -6870,7 +6870,7 @@
         <v>398.8734718832065</v>
       </c>
       <c r="Q34" t="n">
-        <v>206.9542799639633</v>
+        <v>207.1191919192516</v>
       </c>
       <c r="R34" t="n">
         <v>15.2</v>
@@ -6882,19 +6882,19 @@
         <v>15.2</v>
       </c>
       <c r="U34" t="n">
-        <v>203.3</v>
+        <v>203.300000000003</v>
       </c>
       <c r="V34" t="n">
-        <v>391.4</v>
+        <v>203.300000000003</v>
       </c>
       <c r="W34" t="n">
-        <v>391.4</v>
+        <v>203.300000000003</v>
       </c>
       <c r="X34" t="n">
-        <v>391.4</v>
+        <v>203.300000000003</v>
       </c>
       <c r="Y34" t="n">
-        <v>567.1593006790322</v>
+        <v>203.300000000003</v>
       </c>
     </row>
     <row r="35">
@@ -6937,16 +6937,16 @@
         <v>264.1600284404761</v>
       </c>
       <c r="M35" t="n">
-        <v>342.2245487608371</v>
+        <v>264.1600284404761</v>
       </c>
       <c r="N35" t="n">
-        <v>342.2245487608371</v>
+        <v>264.1600284404761</v>
       </c>
       <c r="O35" t="n">
-        <v>404.1105430081138</v>
+        <v>326.0460226877527</v>
       </c>
       <c r="P35" t="n">
-        <v>516</v>
+        <v>437.9354796796389</v>
       </c>
       <c r="Q35" t="n">
         <v>516</v>
@@ -6955,25 +6955,25 @@
         <v>516</v>
       </c>
       <c r="S35" t="n">
-        <v>516</v>
+        <v>503.9868768455294</v>
       </c>
       <c r="T35" t="n">
-        <v>396.5794184864514</v>
+        <v>384.5662953319808</v>
       </c>
       <c r="U35" t="n">
-        <v>269.1905388491649</v>
+        <v>384.5662953319808</v>
       </c>
       <c r="V35" t="n">
-        <v>269.1905388491649</v>
+        <v>333.1468475748655</v>
       </c>
       <c r="W35" t="n">
-        <v>138.887508546129</v>
+        <v>202.8438172717663</v>
       </c>
       <c r="X35" t="n">
-        <v>10.32</v>
+        <v>74.27630872563728</v>
       </c>
       <c r="Y35" t="n">
-        <v>10.32</v>
+        <v>27.491023187449</v>
       </c>
     </row>
     <row r="36">
@@ -6983,19 +6983,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>140.6230303030358</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="C36" t="n">
-        <v>140.6230303030358</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="D36" t="n">
-        <v>140.6230303030358</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="E36" t="n">
-        <v>140.6230303030358</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="F36" t="n">
-        <v>140.6230303030358</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="G36" t="n">
         <v>140.6230303030358</v>
@@ -7007,10 +7007,10 @@
         <v>10.32</v>
       </c>
       <c r="J36" t="n">
-        <v>138.0300000000054</v>
+        <v>10.32</v>
       </c>
       <c r="K36" t="n">
-        <v>138.0300000000054</v>
+        <v>10.32</v>
       </c>
       <c r="L36" t="n">
         <v>138.0300000000054</v>
@@ -7019,7 +7019,7 @@
         <v>260.5799999999891</v>
       </c>
       <c r="N36" t="n">
-        <v>260.5799999999891</v>
+        <v>388.2899999999946</v>
       </c>
       <c r="O36" t="n">
         <v>388.2899999999946</v>
@@ -7028,31 +7028,31 @@
         <v>516</v>
       </c>
       <c r="Q36" t="n">
-        <v>516</v>
+        <v>395.5309881876231</v>
       </c>
       <c r="R36" t="n">
-        <v>459.334795950141</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="S36" t="n">
-        <v>329.0317656471107</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="T36" t="n">
-        <v>329.0317656471107</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="U36" t="n">
-        <v>329.0317656471107</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="V36" t="n">
-        <v>329.0317656471107</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="W36" t="n">
-        <v>270.9260606060661</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="X36" t="n">
-        <v>270.9260606060661</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="Y36" t="n">
-        <v>140.6230303030358</v>
+        <v>270.9260606060717</v>
       </c>
     </row>
     <row r="37">
@@ -7062,22 +7062,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>132.8700000000001</v>
+        <v>132.8699999999837</v>
       </c>
       <c r="C37" t="n">
-        <v>132.8700000000001</v>
+        <v>132.8699999999837</v>
       </c>
       <c r="D37" t="n">
-        <v>260.58</v>
+        <v>132.8699999999837</v>
       </c>
       <c r="E37" t="n">
-        <v>388.29</v>
+        <v>260.5799999999891</v>
       </c>
       <c r="F37" t="n">
-        <v>388.29</v>
+        <v>388.2899999999946</v>
       </c>
       <c r="G37" t="n">
-        <v>388.29</v>
+        <v>516</v>
       </c>
       <c r="H37" t="n">
         <v>516</v>
@@ -7098,16 +7098,16 @@
         <v>515.7698245478466</v>
       </c>
       <c r="N37" t="n">
-        <v>515.7698245478466</v>
+        <v>463.1448602893141</v>
       </c>
       <c r="O37" t="n">
-        <v>389.0142125455297</v>
+        <v>336.3892482869973</v>
       </c>
       <c r="P37" t="n">
-        <v>270.9260606060606</v>
+        <v>270.926060606228</v>
       </c>
       <c r="Q37" t="n">
-        <v>140.6230303030303</v>
+        <v>140.6230303031128</v>
       </c>
       <c r="R37" t="n">
         <v>10.32</v>
@@ -7116,22 +7116,22 @@
         <v>118.0182006679436</v>
       </c>
       <c r="T37" t="n">
-        <v>118.0182006679436</v>
+        <v>132.8699999999837</v>
       </c>
       <c r="U37" t="n">
-        <v>118.0182006679436</v>
+        <v>132.8699999999837</v>
       </c>
       <c r="V37" t="n">
-        <v>118.0182006679436</v>
+        <v>132.8699999999837</v>
       </c>
       <c r="W37" t="n">
-        <v>118.0182006679436</v>
+        <v>132.8699999999837</v>
       </c>
       <c r="X37" t="n">
-        <v>132.8700000000001</v>
+        <v>132.8699999999837</v>
       </c>
       <c r="Y37" t="n">
-        <v>132.8700000000001</v>
+        <v>132.8699999999837</v>
       </c>
     </row>
     <row r="38">
@@ -7174,7 +7174,7 @@
         <v>264.1600284404761</v>
       </c>
       <c r="M38" t="n">
-        <v>264.1600284404761</v>
+        <v>342.2245487608371</v>
       </c>
       <c r="N38" t="n">
         <v>342.2245487608371</v>
@@ -7195,22 +7195,22 @@
         <v>503.9868768455294</v>
       </c>
       <c r="T38" t="n">
-        <v>384.5662953319808</v>
+        <v>465.1853996350185</v>
       </c>
       <c r="U38" t="n">
-        <v>254.2632650289412</v>
+        <v>334.8823693318776</v>
       </c>
       <c r="V38" t="n">
-        <v>123.9602347259017</v>
+        <v>204.579339028762</v>
       </c>
       <c r="W38" t="n">
-        <v>10.32</v>
+        <v>74.27630872563728</v>
       </c>
       <c r="X38" t="n">
-        <v>10.32</v>
+        <v>74.27630872563728</v>
       </c>
       <c r="Y38" t="n">
-        <v>10.32</v>
+        <v>27.491023187449</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>270.9260606060606</v>
+        <v>338.865784137764</v>
       </c>
       <c r="C39" t="n">
-        <v>270.9260606060606</v>
+        <v>338.865784137764</v>
       </c>
       <c r="D39" t="n">
-        <v>140.6230303030303</v>
+        <v>338.865784137764</v>
       </c>
       <c r="E39" t="n">
-        <v>140.6230303030303</v>
+        <v>338.865784137764</v>
       </c>
       <c r="F39" t="n">
-        <v>140.6230303030303</v>
+        <v>208.5627538347245</v>
       </c>
       <c r="G39" t="n">
-        <v>140.6230303030303</v>
+        <v>78.25972353168498</v>
       </c>
       <c r="H39" t="n">
         <v>10.32</v>
@@ -7244,19 +7244,19 @@
         <v>10.32</v>
       </c>
       <c r="J39" t="n">
-        <v>10.32</v>
+        <v>138.030000000009</v>
       </c>
       <c r="K39" t="n">
-        <v>10.32</v>
+        <v>265.7400000000181</v>
       </c>
       <c r="L39" t="n">
-        <v>138.030000000009</v>
+        <v>393.4500000000271</v>
       </c>
       <c r="M39" t="n">
-        <v>260.579999999991</v>
+        <v>393.4500000000271</v>
       </c>
       <c r="N39" t="n">
-        <v>388.289999999991</v>
+        <v>393.4500000000271</v>
       </c>
       <c r="O39" t="n">
         <v>516</v>
@@ -7265,31 +7265,31 @@
         <v>516</v>
       </c>
       <c r="Q39" t="n">
-        <v>401.2290909090909</v>
+        <v>395.5309881876231</v>
       </c>
       <c r="R39" t="n">
-        <v>270.9260606060606</v>
+        <v>338.865784137764</v>
       </c>
       <c r="S39" t="n">
-        <v>270.9260606060606</v>
+        <v>338.865784137764</v>
       </c>
       <c r="T39" t="n">
-        <v>270.9260606060606</v>
+        <v>338.865784137764</v>
       </c>
       <c r="U39" t="n">
-        <v>270.9260606060606</v>
+        <v>338.865784137764</v>
       </c>
       <c r="V39" t="n">
-        <v>270.9260606060606</v>
+        <v>338.865784137764</v>
       </c>
       <c r="W39" t="n">
-        <v>270.9260606060606</v>
+        <v>338.865784137764</v>
       </c>
       <c r="X39" t="n">
-        <v>270.9260606060606</v>
+        <v>338.865784137764</v>
       </c>
       <c r="Y39" t="n">
-        <v>270.9260606060606</v>
+        <v>338.865784137764</v>
       </c>
     </row>
     <row r="40">
@@ -7299,31 +7299,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>260.58</v>
+        <v>138.030000000009</v>
       </c>
       <c r="C40" t="n">
-        <v>260.58</v>
+        <v>138.030000000009</v>
       </c>
       <c r="D40" t="n">
-        <v>260.58</v>
+        <v>265.7400000000181</v>
       </c>
       <c r="E40" t="n">
-        <v>260.58</v>
+        <v>265.7400000000181</v>
       </c>
       <c r="F40" t="n">
-        <v>260.58</v>
+        <v>265.7400000000181</v>
       </c>
       <c r="G40" t="n">
-        <v>260.58</v>
+        <v>265.7400000000181</v>
       </c>
       <c r="H40" t="n">
-        <v>388.29</v>
+        <v>388.289999999991</v>
       </c>
       <c r="I40" t="n">
-        <v>388.29</v>
+        <v>388.289999999991</v>
       </c>
       <c r="J40" t="n">
-        <v>388.29</v>
+        <v>388.289999999991</v>
       </c>
       <c r="K40" t="n">
         <v>516</v>
@@ -7338,13 +7338,13 @@
         <v>463.1448602893141</v>
       </c>
       <c r="O40" t="n">
-        <v>401.2290909090909</v>
+        <v>336.3892482869973</v>
       </c>
       <c r="P40" t="n">
-        <v>270.9260606060606</v>
+        <v>206.0862179838483</v>
       </c>
       <c r="Q40" t="n">
-        <v>140.6230303030303</v>
+        <v>75.78318768069951</v>
       </c>
       <c r="R40" t="n">
         <v>10.32</v>
@@ -7356,19 +7356,19 @@
         <v>10.32</v>
       </c>
       <c r="U40" t="n">
-        <v>138.03</v>
+        <v>10.32</v>
       </c>
       <c r="V40" t="n">
-        <v>138.03</v>
+        <v>10.32</v>
       </c>
       <c r="W40" t="n">
-        <v>138.03</v>
+        <v>138.030000000009</v>
       </c>
       <c r="X40" t="n">
-        <v>138.03</v>
+        <v>138.030000000009</v>
       </c>
       <c r="Y40" t="n">
-        <v>138.03</v>
+        <v>138.030000000009</v>
       </c>
     </row>
     <row r="41">
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>255.3939393939063</v>
+        <v>10.32</v>
       </c>
       <c r="C41" t="n">
-        <v>255.3939393939063</v>
+        <v>10.32</v>
       </c>
       <c r="D41" t="n">
-        <v>255.3939393939063</v>
+        <v>10.32</v>
       </c>
       <c r="E41" t="n">
-        <v>255.3939393939063</v>
+        <v>10.32</v>
       </c>
       <c r="F41" t="n">
-        <v>140.6230303030469</v>
+        <v>10.32</v>
       </c>
       <c r="G41" t="n">
         <v>10.32</v>
@@ -7402,13 +7402,13 @@
         <v>10.32</v>
       </c>
       <c r="J41" t="n">
-        <v>91.4151827306864</v>
+        <v>41.83406683243596</v>
       </c>
       <c r="K41" t="n">
-        <v>219.1251827306864</v>
+        <v>141.0606624103254</v>
       </c>
       <c r="L41" t="n">
-        <v>342.2245487608371</v>
+        <v>264.1600284404761</v>
       </c>
       <c r="M41" t="n">
         <v>342.2245487608371</v>
@@ -7432,22 +7432,22 @@
         <v>516</v>
       </c>
       <c r="T41" t="n">
-        <v>516</v>
+        <v>385.6969696967699</v>
       </c>
       <c r="U41" t="n">
-        <v>516</v>
+        <v>255.393939393723</v>
       </c>
       <c r="V41" t="n">
-        <v>385.6969696969531</v>
+        <v>125.0909090906761</v>
       </c>
       <c r="W41" t="n">
-        <v>255.3939393939063</v>
+        <v>10.32</v>
       </c>
       <c r="X41" t="n">
-        <v>255.3939393939063</v>
+        <v>10.32</v>
       </c>
       <c r="Y41" t="n">
-        <v>255.3939393939063</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>192.9145068351761</v>
+        <v>231.5701003466888</v>
       </c>
       <c r="C42" t="n">
-        <v>192.9145068351761</v>
+        <v>114.2974615128309</v>
       </c>
       <c r="D42" t="n">
-        <v>192.9145068351761</v>
+        <v>10.32</v>
       </c>
       <c r="E42" t="n">
-        <v>94.25582277263811</v>
+        <v>10.32</v>
       </c>
       <c r="F42" t="n">
-        <v>94.25582277263811</v>
+        <v>10.32</v>
       </c>
       <c r="G42" t="n">
-        <v>94.25582277263811</v>
+        <v>10.32</v>
       </c>
       <c r="H42" t="n">
         <v>10.32</v>
@@ -7481,22 +7481,22 @@
         <v>10.32</v>
       </c>
       <c r="J42" t="n">
-        <v>10.32</v>
+        <v>138.0300000000162</v>
       </c>
       <c r="K42" t="n">
-        <v>132.8699999999675</v>
+        <v>138.0300000000162</v>
       </c>
       <c r="L42" t="n">
-        <v>260.5799999999838</v>
+        <v>138.0300000000162</v>
       </c>
       <c r="M42" t="n">
-        <v>260.5799999999838</v>
+        <v>138.0300000000162</v>
       </c>
       <c r="N42" t="n">
+        <v>265.7400000000325</v>
+      </c>
+      <c r="O42" t="n">
         <v>388.2899999999838</v>
-      </c>
-      <c r="O42" t="n">
-        <v>516</v>
       </c>
       <c r="P42" t="n">
         <v>516</v>
@@ -7514,19 +7514,19 @@
         <v>516</v>
       </c>
       <c r="U42" t="n">
-        <v>385.6969696967871</v>
+        <v>516</v>
       </c>
       <c r="V42" t="n">
-        <v>323.2175371383353</v>
+        <v>385.6969696968118</v>
       </c>
       <c r="W42" t="n">
-        <v>323.2175371383353</v>
+        <v>385.6969696968118</v>
       </c>
       <c r="X42" t="n">
-        <v>323.2175371383353</v>
+        <v>385.6969696968118</v>
       </c>
       <c r="Y42" t="n">
-        <v>323.2175371383353</v>
+        <v>361.8731306498628</v>
       </c>
     </row>
     <row r="43">
@@ -7536,49 +7536,49 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>158.3658101624804</v>
+        <v>117.939843072223</v>
       </c>
       <c r="C43" t="n">
-        <v>130.3605105179908</v>
+        <v>117.939843072223</v>
       </c>
       <c r="D43" t="n">
-        <v>89.41483571439943</v>
+        <v>117.939843072223</v>
       </c>
       <c r="E43" t="n">
-        <v>53.0704873942413</v>
+        <v>117.939843072223</v>
       </c>
       <c r="F43" t="n">
-        <v>23.39083490157268</v>
+        <v>117.939843072223</v>
       </c>
       <c r="G43" t="n">
-        <v>23.69730898517926</v>
+        <v>118.2463171558296</v>
       </c>
       <c r="H43" t="n">
-        <v>42.87489611178994</v>
+        <v>137.4239042824403</v>
       </c>
       <c r="I43" t="n">
-        <v>121.0804688183647</v>
+        <v>215.629476989015</v>
       </c>
       <c r="J43" t="n">
-        <v>248.7904688183646</v>
+        <v>343.3394769890313</v>
       </c>
       <c r="K43" t="n">
-        <v>248.7904688183646</v>
+        <v>343.3394769890313</v>
       </c>
       <c r="L43" t="n">
-        <v>248.7904688183646</v>
+        <v>216.0663967170569</v>
       </c>
       <c r="M43" t="n">
-        <v>248.7904688183646</v>
+        <v>216.0663967170569</v>
       </c>
       <c r="N43" t="n">
-        <v>118.4874385153343</v>
+        <v>216.0663967170569</v>
       </c>
       <c r="O43" t="n">
-        <v>118.4874385153343</v>
+        <v>140.6230303032436</v>
       </c>
       <c r="P43" t="n">
-        <v>118.4874385153343</v>
+        <v>10.32</v>
       </c>
       <c r="Q43" t="n">
         <v>10.32</v>
@@ -7602,10 +7602,10 @@
         <v>203.3733311394362</v>
       </c>
       <c r="X43" t="n">
-        <v>200.9050024221558</v>
+        <v>203.3733311394362</v>
       </c>
       <c r="Y43" t="n">
-        <v>200.9050024221558</v>
+        <v>160.4790353318984</v>
       </c>
     </row>
     <row r="44">
@@ -7615,19 +7615,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>121.2121212121212</v>
+        <v>10</v>
       </c>
       <c r="C44" t="n">
-        <v>121.2121212121212</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>121.2121212121212</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>121.2121212121212</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
-        <v>121.2121212121212</v>
+        <v>10</v>
       </c>
       <c r="G44" t="n">
         <v>10</v>
@@ -7666,25 +7666,25 @@
         <v>500</v>
       </c>
       <c r="S44" t="n">
-        <v>500</v>
+        <v>373.7373737373379</v>
       </c>
       <c r="T44" t="n">
-        <v>500</v>
+        <v>373.7373737373379</v>
       </c>
       <c r="U44" t="n">
-        <v>373.7373737373737</v>
+        <v>247.4747474746757</v>
       </c>
       <c r="V44" t="n">
-        <v>373.7373737373737</v>
+        <v>136.2626262626621</v>
       </c>
       <c r="W44" t="n">
-        <v>373.7373737373737</v>
+        <v>136.2626262626621</v>
       </c>
       <c r="X44" t="n">
-        <v>247.4747474747475</v>
+        <v>136.2626262626621</v>
       </c>
       <c r="Y44" t="n">
-        <v>121.2121212121212</v>
+        <v>136.2626262626621</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>222.8648028115113</v>
+        <v>405.4593096466874</v>
       </c>
       <c r="C45" t="n">
-        <v>105.5921639776534</v>
+        <v>288.1866708128296</v>
       </c>
       <c r="D45" t="n">
-        <v>105.5921639776534</v>
+        <v>288.1866708128296</v>
       </c>
       <c r="E45" t="n">
-        <v>105.5921639776534</v>
+        <v>189.5279867502915</v>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>93.93582277263812</v>
       </c>
       <c r="G45" t="n">
-        <v>10</v>
+        <v>93.93582277263812</v>
       </c>
       <c r="H45" t="n">
         <v>10</v>
@@ -7724,16 +7724,16 @@
         <v>10</v>
       </c>
       <c r="L45" t="n">
-        <v>133.75</v>
+        <v>10</v>
       </c>
       <c r="M45" t="n">
-        <v>133.75</v>
+        <v>128.7499999999297</v>
       </c>
       <c r="N45" t="n">
-        <v>257.5</v>
+        <v>252.4999999999297</v>
       </c>
       <c r="O45" t="n">
-        <v>381.25</v>
+        <v>376.2499999999649</v>
       </c>
       <c r="P45" t="n">
         <v>500</v>
@@ -7751,19 +7751,19 @@
         <v>500</v>
       </c>
       <c r="U45" t="n">
-        <v>373.7373737373737</v>
+        <v>500</v>
       </c>
       <c r="V45" t="n">
-        <v>373.7373737373737</v>
+        <v>500</v>
       </c>
       <c r="W45" t="n">
-        <v>373.7373737373737</v>
+        <v>500</v>
       </c>
       <c r="X45" t="n">
-        <v>349.1274290741376</v>
+        <v>500</v>
       </c>
       <c r="Y45" t="n">
-        <v>222.8648028115113</v>
+        <v>500</v>
       </c>
     </row>
     <row r="46">
@@ -7773,55 +7773,55 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>153.4229304460857</v>
+        <v>203.0533311394362</v>
       </c>
       <c r="C46" t="n">
-        <v>153.4229304460857</v>
+        <v>203.0533311394362</v>
       </c>
       <c r="D46" t="n">
-        <v>153.4229304460857</v>
+        <v>203.0533311394362</v>
       </c>
       <c r="E46" t="n">
-        <v>153.4229304460857</v>
+        <v>203.0533311394362</v>
       </c>
       <c r="F46" t="n">
-        <v>153.4229304460857</v>
+        <v>203.0533311394362</v>
       </c>
       <c r="G46" t="n">
-        <v>153.7294045296923</v>
+        <v>203.3598052230427</v>
       </c>
       <c r="H46" t="n">
-        <v>172.906991656303</v>
+        <v>222.5373923496534</v>
       </c>
       <c r="I46" t="n">
-        <v>251.1125643628777</v>
+        <v>300.7429650562282</v>
       </c>
       <c r="J46" t="n">
-        <v>374.8625643628777</v>
+        <v>424.4929650562282</v>
       </c>
       <c r="K46" t="n">
-        <v>374.8625643628777</v>
+        <v>424.4929650562282</v>
       </c>
       <c r="L46" t="n">
-        <v>374.8625643628777</v>
+        <v>424.4929650562282</v>
       </c>
       <c r="M46" t="n">
-        <v>248.5999381002514</v>
+        <v>298.2303387936019</v>
       </c>
       <c r="N46" t="n">
-        <v>248.5999381002514</v>
+        <v>298.2303387936019</v>
       </c>
       <c r="O46" t="n">
-        <v>248.5999381002514</v>
+        <v>171.9677125309756</v>
       </c>
       <c r="P46" t="n">
-        <v>122.3373118376252</v>
+        <v>171.9677125309756</v>
       </c>
       <c r="Q46" t="n">
-        <v>122.3373118376252</v>
+        <v>171.9677125309756</v>
       </c>
       <c r="R46" t="n">
-        <v>122.3373118376252</v>
+        <v>45.70508626834936</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -7842,7 +7842,7 @@
         <v>203.0533311394362</v>
       </c>
       <c r="Y46" t="n">
-        <v>160.1590353318985</v>
+        <v>203.0533311394362</v>
       </c>
     </row>
   </sheetData>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>465.3046760599197</v>
+        <v>405.9068110594027</v>
       </c>
       <c r="N2" t="n">
         <v>336.654907818579</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>87.73406121190752</v>
+        <v>147.1319262124245</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8043,22 +8043,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J3" t="n">
-        <v>186.4256073882259</v>
+        <v>62.42560738822591</v>
       </c>
       <c r="K3" t="n">
-        <v>160.6996692410901</v>
+        <v>155.6895682309891</v>
       </c>
       <c r="L3" t="n">
-        <v>146.4604139412998</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M3" t="n">
-        <v>277.9247782656032</v>
+        <v>401.9247782656032</v>
       </c>
       <c r="N3" t="n">
-        <v>360.1246685054247</v>
+        <v>365.1347695155256</v>
       </c>
       <c r="O3" t="n">
-        <v>40.91900331325166</v>
+        <v>164.9190033132516</v>
       </c>
       <c r="P3" t="n">
         <v>24.9804809108019</v>
@@ -8201,7 +8201,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>48.41751852767479</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -8219,10 +8219,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>10.98034647284221</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>87.73406121190752</v>
+        <v>147.1319262124245</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8280,19 +8280,19 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J6" t="n">
-        <v>181.4155063781249</v>
+        <v>186.4256073882259</v>
       </c>
       <c r="K6" t="n">
-        <v>160.6996692410901</v>
+        <v>36.69966924109012</v>
       </c>
       <c r="L6" t="n">
-        <v>146.4604139412998</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M6" t="n">
-        <v>277.9247782656032</v>
+        <v>401.9247782656032</v>
       </c>
       <c r="N6" t="n">
-        <v>241.1347695155256</v>
+        <v>360.1246685054247</v>
       </c>
       <c r="O6" t="n">
         <v>40.91900331325166</v>
@@ -8441,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>83.43890941450616</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>87.73406121190752</v>
+        <v>171.1729706264136</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8517,22 +8517,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J9" t="n">
-        <v>227.4647419277884</v>
+        <v>62.42560738822591</v>
       </c>
       <c r="K9" t="n">
-        <v>295.8802408630135</v>
+        <v>36.69966924109012</v>
       </c>
       <c r="L9" t="n">
-        <v>22.46041394129978</v>
+        <v>285.4604139412998</v>
       </c>
       <c r="M9" t="n">
-        <v>471.6948204301074</v>
+        <v>354.8545270537683</v>
       </c>
       <c r="N9" t="n">
-        <v>241.1347695155256</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O9" t="n">
-        <v>270.1327614312514</v>
+        <v>303.9190033132517</v>
       </c>
       <c r="P9" t="n">
         <v>219.1507118405495</v>
@@ -8675,22 +8675,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>292.1676092601657</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>199.6572060301507</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>729.9068110594033</v>
+        <v>729.9068110594028</v>
       </c>
       <c r="N11" t="n">
-        <v>660.6549078185795</v>
+        <v>571.461561508273</v>
       </c>
       <c r="O11" t="n">
-        <v>3.317056919707838</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -8757,10 +8757,10 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K12" t="n">
-        <v>198.3555948605421</v>
+        <v>36.69966924109012</v>
       </c>
       <c r="L12" t="n">
-        <v>22.46041394129978</v>
+        <v>346.4604139412998</v>
       </c>
       <c r="M12" t="n">
         <v>471.6948204301074</v>
@@ -8772,7 +8772,7 @@
         <v>364.9190033132517</v>
       </c>
       <c r="P12" t="n">
-        <v>219.1507118405495</v>
+        <v>56.8066374600014</v>
       </c>
       <c r="Q12" t="n">
         <v>17.27519534353338</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>292.1676092601657</v>
       </c>
       <c r="K14" t="n">
-        <v>202.9742629498585</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>729.9068110594033</v>
+        <v>729.9068110594028</v>
       </c>
       <c r="N14" t="n">
-        <v>660.6549078185795</v>
+        <v>571.461561508273</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L15" t="n">
-        <v>22.46041394129978</v>
+        <v>248.9357679388284</v>
       </c>
       <c r="M15" t="n">
         <v>471.6948204301074</v>
@@ -9006,7 +9006,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O15" t="n">
-        <v>267.3943573107802</v>
+        <v>40.91900331325166</v>
       </c>
       <c r="P15" t="n">
         <v>219.1507118405495</v>
@@ -9149,7 +9149,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>202.9742629498585</v>
+        <v>292.1676092601657</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -9158,10 +9158,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>729.9068110594033</v>
+        <v>729.9068110594028</v>
       </c>
       <c r="N17" t="n">
-        <v>660.6549078185795</v>
+        <v>571.461561508273</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9231,13 +9231,13 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K18" t="n">
-        <v>295.8802408630135</v>
+        <v>36.69966924109012</v>
       </c>
       <c r="L18" t="n">
-        <v>22.46041394129978</v>
+        <v>346.4604139412998</v>
       </c>
       <c r="M18" t="n">
-        <v>374.170174427636</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N18" t="n">
         <v>485.4085271713503</v>
@@ -9246,7 +9246,7 @@
         <v>364.9190033132517</v>
       </c>
       <c r="P18" t="n">
-        <v>219.1507118405495</v>
+        <v>56.8066374600014</v>
       </c>
       <c r="Q18" t="n">
         <v>17.27519534353338</v>
@@ -9386,7 +9386,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>296.1676092601662</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -9395,19 +9395,19 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>405.9068110594027</v>
+        <v>733.9068110594033</v>
       </c>
       <c r="N20" t="n">
         <v>664.6549078185794</v>
       </c>
       <c r="O20" t="n">
-        <v>242.6450375280768</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>87.73406121190752</v>
+        <v>298.5467080001501</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9465,22 +9465,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J21" t="n">
-        <v>62.42560738822591</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K21" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L21" t="n">
-        <v>346.0870439725993</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M21" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N21" t="n">
-        <v>241.1347695155256</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O21" t="n">
-        <v>368.9190033132517</v>
+        <v>283.2327411491641</v>
       </c>
       <c r="P21" t="n">
         <v>219.1507118405495</v>
@@ -9626,22 +9626,22 @@
         <v>367.1676092601664</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>298.7711155778894</v>
       </c>
       <c r="L23" t="n">
-        <v>95.79600418654661</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>405.9068110594027</v>
       </c>
       <c r="N23" t="n">
-        <v>336.654907818579</v>
+        <v>419.6601429000791</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>285.9803464728429</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>486.7340612119082</v>
@@ -9702,16 +9702,16 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J24" t="n">
-        <v>62.42560738822591</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K24" t="n">
-        <v>276.9727083636511</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L24" t="n">
         <v>388.0893364597981</v>
       </c>
       <c r="M24" t="n">
-        <v>471.6948204301074</v>
+        <v>287.7481533911825</v>
       </c>
       <c r="N24" t="n">
         <v>485.4085271713503</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>296.1676092601658</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>203.6572060301507</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>733.9068110594028</v>
       </c>
       <c r="N26" t="n">
-        <v>336.654907818579</v>
+        <v>664.654907818579</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>126.7218927098346</v>
+        <v>298.5467080001511</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9939,13 +9939,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J27" t="n">
-        <v>62.42560738822591</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K27" t="n">
-        <v>241.403344168236</v>
+        <v>210.1939786989259</v>
       </c>
       <c r="L27" t="n">
-        <v>350.4604139412998</v>
+        <v>350.4604139412999</v>
       </c>
       <c r="M27" t="n">
         <v>471.6948204301074</v>
@@ -9954,10 +9954,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O27" t="n">
-        <v>368.9190033132517</v>
+        <v>40.91900331325166</v>
       </c>
       <c r="P27" t="n">
-        <v>24.9804809108019</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q27" t="n">
         <v>17.27519534353338</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>296.1676092601667</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>227.7711155778894</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>533.8003865367468</v>
+        <v>733.9068110594037</v>
       </c>
       <c r="N29" t="n">
-        <v>336.654907818579</v>
+        <v>664.6549078185799</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>214.9803464728432</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>87.73406121190752</v>
+        <v>298.5467080001492</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10182,16 +10182,16 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L30" t="n">
-        <v>350.4604139412998</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M30" t="n">
-        <v>302.2823159218444</v>
+        <v>386.0085582660189</v>
       </c>
       <c r="N30" t="n">
-        <v>241.1347695155256</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O30" t="n">
-        <v>368.9190033132517</v>
+        <v>368.9190033132527</v>
       </c>
       <c r="P30" t="n">
         <v>219.1507118405495</v>
@@ -10349,13 +10349,13 @@
         <v>336.654907818579</v>
       </c>
       <c r="O32" t="n">
-        <v>127.4888946997236</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.899509664274333</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>87.73406121190752</v>
+        <v>218.1224655759055</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10416,22 +10416,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K33" t="n">
-        <v>36.69966924109012</v>
+        <v>226.6996692410932</v>
       </c>
       <c r="L33" t="n">
-        <v>22.46041394129978</v>
+        <v>212.4604139413028</v>
       </c>
       <c r="M33" t="n">
-        <v>467.9247782656032</v>
+        <v>295.2088760492639</v>
       </c>
       <c r="N33" t="n">
-        <v>431.1347695155256</v>
+        <v>241.1347695155256</v>
       </c>
       <c r="O33" t="n">
-        <v>230.9190033132516</v>
+        <v>40.91900331325166</v>
       </c>
       <c r="P33" t="n">
-        <v>42.26457869447174</v>
+        <v>214.9804809108049</v>
       </c>
       <c r="Q33" t="n">
         <v>17.27519534353338</v>
@@ -10580,7 +10580,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>484.7598618880502</v>
+        <v>405.9068110594027</v>
       </c>
       <c r="N35" t="n">
         <v>336.654907818579</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>87.73406121190752</v>
+        <v>166.587112040555</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10650,22 +10650,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>191.4256073882314</v>
+        <v>62.42560738822591</v>
       </c>
       <c r="K36" t="n">
         <v>36.69966924109012</v>
       </c>
       <c r="L36" t="n">
-        <v>22.46041394129978</v>
+        <v>151.4604139413053</v>
       </c>
       <c r="M36" t="n">
         <v>401.7126570534655</v>
       </c>
       <c r="N36" t="n">
-        <v>241.1347695155256</v>
+        <v>370.134769515531</v>
       </c>
       <c r="O36" t="n">
-        <v>169.9190033132572</v>
+        <v>40.91900331325166</v>
       </c>
       <c r="P36" t="n">
         <v>153.9804809108074</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>405.9068110594027</v>
+        <v>484.7598618880502</v>
       </c>
       <c r="N38" t="n">
-        <v>415.5079586472265</v>
+        <v>336.654907818579</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10887,22 +10887,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>62.42560738822591</v>
+        <v>191.425607388235</v>
       </c>
       <c r="K39" t="n">
-        <v>36.69966924109012</v>
+        <v>165.6996692410993</v>
       </c>
       <c r="L39" t="n">
         <v>151.4604139413089</v>
       </c>
       <c r="M39" t="n">
-        <v>401.7126570534637</v>
+        <v>277.9247782656032</v>
       </c>
       <c r="N39" t="n">
-        <v>370.1347695155256</v>
+        <v>241.1347695155256</v>
       </c>
       <c r="O39" t="n">
-        <v>169.9190033132608</v>
+        <v>164.7068821011031</v>
       </c>
       <c r="P39" t="n">
         <v>24.9804809108019</v>
@@ -11045,16 +11045,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>50.08193525075805</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>28.77111557788945</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>405.9068110594027</v>
+        <v>484.7598618880502</v>
       </c>
       <c r="N41" t="n">
         <v>336.654907818579</v>
@@ -11124,25 +11124,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>62.42560738822591</v>
+        <v>191.4256073882423</v>
       </c>
       <c r="K42" t="n">
-        <v>160.4875480289361</v>
+        <v>36.69966924109012</v>
       </c>
       <c r="L42" t="n">
-        <v>151.4604139413162</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M42" t="n">
         <v>277.9247782656032</v>
       </c>
       <c r="N42" t="n">
-        <v>370.1347695155256</v>
+        <v>370.134769515542</v>
       </c>
       <c r="O42" t="n">
-        <v>169.9190033132681</v>
+        <v>164.7068821010813</v>
       </c>
       <c r="P42" t="n">
-        <v>24.9804809108019</v>
+        <v>153.9804809108183</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11367,19 +11367,19 @@
         <v>36.69966924109012</v>
       </c>
       <c r="L45" t="n">
-        <v>147.4604139412998</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M45" t="n">
-        <v>277.9247782656032</v>
+        <v>397.8742732150271</v>
       </c>
       <c r="N45" t="n">
         <v>366.1347695155256</v>
       </c>
       <c r="O45" t="n">
-        <v>165.9190033132516</v>
+        <v>165.9190033132872</v>
       </c>
       <c r="P45" t="n">
-        <v>144.9299758602968</v>
+        <v>149.9804809108374</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22515,7 +22515,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -22566,7 +22566,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>59.22637569841311</v>
+        <v>183.2263756984131</v>
       </c>
       <c r="U2" t="n">
         <v>249.1582613727313</v>
@@ -22575,10 +22575,10 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>238.3734759809475</v>
+        <v>223.4000984285024</v>
       </c>
       <c r="X2" t="n">
-        <v>127.8338776652286</v>
+        <v>68.28183346066771</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -22715,10 +22715,10 @@
         <v>120.7006186397529</v>
       </c>
       <c r="Q4" t="n">
-        <v>296.243266425598</v>
+        <v>245.3506547391771</v>
       </c>
       <c r="R4" t="n">
-        <v>259.8174507209596</v>
+        <v>310.7100624073805</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22752,7 +22752,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984979</v>
@@ -22764,7 +22764,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.969432588523748</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -22806,19 +22806,19 @@
         <v>183.2263756984131</v>
       </c>
       <c r="U5" t="n">
-        <v>188.9534232019359</v>
+        <v>149.1919796876118</v>
       </c>
       <c r="V5" t="n">
         <v>105.8510241668239</v>
       </c>
       <c r="W5" t="n">
-        <v>238.3734759809475</v>
+        <v>114.3734759809475</v>
       </c>
       <c r="X5" t="n">
         <v>68.28183346066771</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -22940,22 +22940,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>65.22787369763185</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>190.4880558822936</v>
+        <v>66.48805588229362</v>
       </c>
       <c r="P7" t="n">
         <v>120.7006186397529</v>
       </c>
       <c r="Q7" t="n">
-        <v>172.243266425598</v>
+        <v>296.243266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>194.5895770233278</v>
+        <v>259.8174507209596</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -22989,16 +22989,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>46.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>5.738210685083043</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -23040,7 +23040,7 @@
         <v>73.89299192292592</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>55.4657072429575</v>
       </c>
       <c r="U8" t="n">
         <v>246.1582613727313</v>
@@ -23177,10 +23177,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>62.22787369763186</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>48.63698913799378</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -23189,7 +23189,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.243266425598</v>
+        <v>141.1081292612236</v>
       </c>
       <c r="R10" t="n">
         <v>44.71006240738057</v>
@@ -23223,22 +23223,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>130.4891052670715</v>
+        <v>173.9993129555745</v>
       </c>
       <c r="C11" t="n">
         <v>141.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>102.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>96.36328960686865</v>
       </c>
       <c r="F11" t="n">
         <v>96.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>94.96943258852374</v>
+        <v>94.96943258852377</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -23277,19 +23277,19 @@
         <v>168.8929919229259</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>275.2263756984131</v>
       </c>
       <c r="U11" t="n">
-        <v>17.15826137271824</v>
+        <v>17.15826137273126</v>
       </c>
       <c r="V11" t="n">
-        <v>321.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>6.373475980936632</v>
+        <v>6.373475980947546</v>
       </c>
       <c r="X11" t="n">
-        <v>284.2818334606677</v>
+        <v>88.69382889383317</v>
       </c>
       <c r="Y11" t="n">
         <v>203.3174326828064</v>
@@ -23350,7 +23350,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.748556743253999</v>
+        <v>1.748556743254028</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -23417,22 +23417,22 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>209.0987146159472</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>230.037697688933</v>
+        <v>12.70061863975292</v>
       </c>
       <c r="Q13" t="n">
-        <v>64.24326642559799</v>
+        <v>166.6790600907254</v>
       </c>
       <c r="R13" t="n">
-        <v>78.71006240738058</v>
+        <v>402.7100624073805</v>
       </c>
       <c r="S13" t="n">
-        <v>48.21393871924888</v>
+        <v>48.21393871924886</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23463,22 +23463,22 @@
         <v>173.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>141.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>102.3391557398498</v>
       </c>
       <c r="E14" t="n">
         <v>96.36328960686865</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>96.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>94.96943258852374</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>91.94017126634148</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23514,19 +23514,19 @@
         <v>168.8929919229259</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>271.9800333259048</v>
       </c>
       <c r="U14" t="n">
-        <v>341.1582613727313</v>
+        <v>17.15826137273127</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>330.3734759809475</v>
+        <v>6.373475980947546</v>
       </c>
       <c r="X14" t="n">
-        <v>151.5929998716256</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>203.3174326828064</v>
@@ -23587,7 +23587,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.748556743254028</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -23602,7 +23602,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.748556743253886</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -23660,16 +23660,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12.70061863975292</v>
+        <v>12.7006186397529</v>
       </c>
       <c r="Q16" t="n">
-        <v>388.243266425598</v>
+        <v>166.6790600907254</v>
       </c>
       <c r="R16" t="n">
-        <v>181.1458560725079</v>
+        <v>402.7100624073806</v>
       </c>
       <c r="S16" t="n">
-        <v>48.21393871924886</v>
+        <v>48.21393871924888</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23697,13 +23697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>86.99931295557451</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>54.47457824299391</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>15.33915573984979</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -23754,7 +23754,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>50.41593093281219</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -23763,10 +23763,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>197.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>90.88471745506165</v>
       </c>
     </row>
     <row r="18">
@@ -23934,10 +23934,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>86.99931295557451</v>
       </c>
       <c r="C20" t="n">
-        <v>34.89273093281236</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -23949,10 +23949,10 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>7.969432588523773</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4.940171266341508</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23988,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>132.2656475830402</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -24000,7 +24000,7 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>197.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -24420,7 +24420,7 @@
         <v>97.36328960686865</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>97.88962870801186</v>
       </c>
       <c r="G26" t="n">
         <v>95.96943258852374</v>
@@ -24465,19 +24465,19 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>14.15826137271529</v>
+        <v>47.69266167688852</v>
       </c>
       <c r="V26" t="n">
         <v>322.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>3.373475980935268</v>
+        <v>3.373475980935723</v>
       </c>
       <c r="X26" t="n">
-        <v>212.3884297900469</v>
+        <v>285.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>204.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -24596,10 +24596,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>64.00034946925459</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>36.33677919164114</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -24608,13 +24608,13 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>337.7006186397529</v>
+        <v>9.700618639739332</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.24326642559799</v>
+        <v>161.5803950865074</v>
       </c>
       <c r="R28" t="n">
-        <v>75.71006240738058</v>
+        <v>403.7100624073806</v>
       </c>
       <c r="S28" t="n">
         <v>49.21393871924888</v>
@@ -24654,16 +24654,16 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>97.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>97.88962870801186</v>
       </c>
       <c r="G29" t="n">
         <v>95.96943258852374</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>92.94017126634148</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24699,22 +24699,22 @@
         <v>169.8929919229259</v>
       </c>
       <c r="T29" t="n">
-        <v>276.2263756984131</v>
+        <v>85.51415560512979</v>
       </c>
       <c r="U29" t="n">
-        <v>14.15826137270801</v>
+        <v>14.15826137270756</v>
       </c>
       <c r="V29" t="n">
-        <v>322.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>267.6025874455167</v>
+        <v>3.373475980928447</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>285.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>204.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -24772,7 +24772,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.225356743253883</v>
+        <v>1.225356743242827</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -24833,28 +24833,28 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>64.00034946925459</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>158.2278736976318</v>
       </c>
       <c r="N31" t="n">
-        <v>36.33677919168699</v>
+        <v>210.0987146159472</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>9.700618639726372</v>
+        <v>118.9250977063675</v>
       </c>
       <c r="Q31" t="n">
-        <v>389.243266425598</v>
+        <v>61.24326642556889</v>
       </c>
       <c r="R31" t="n">
-        <v>75.71006240736119</v>
+        <v>75.71006240736074</v>
       </c>
       <c r="S31" t="n">
-        <v>49.21393871924888</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24882,7 +24882,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>16.99931295557451</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -24933,13 +24933,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>11.89299192292594</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>76.85640336238993</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -24948,7 +24948,7 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>105.7487082408905</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -25085,10 +25085,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>41.24326642554729</v>
+        <v>41.40652926128271</v>
       </c>
       <c r="R34" t="n">
-        <v>55.87332524305683</v>
+        <v>55.7100624073214</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -25119,7 +25119,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -25170,25 +25170,25 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>11.89299192292594</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>58.04327053181764</v>
+        <v>184.1582613727313</v>
       </c>
       <c r="V35" t="n">
-        <v>164.8510241668239</v>
+        <v>113.9457708872798</v>
       </c>
       <c r="W35" t="n">
-        <v>44.37347598094203</v>
+        <v>44.37347598087933</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>46.31743268280638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -25313,19 +25313,19 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>52.09871461594719</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>62.79334821967842</v>
+        <v>114.8920628357913</v>
       </c>
       <c r="Q37" t="n">
-        <v>102.243266425598</v>
+        <v>102.2432664255139</v>
       </c>
       <c r="R37" t="n">
-        <v>116.7100624073805</v>
+        <v>116.7100624072989</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -25410,22 +25410,22 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>79.81291326000736</v>
       </c>
       <c r="U38" t="n">
-        <v>55.15826137272217</v>
+        <v>55.15826137262184</v>
       </c>
       <c r="V38" t="n">
-        <v>35.8510241668148</v>
+        <v>35.85102416673942</v>
       </c>
       <c r="W38" t="n">
-        <v>60.86964360230483</v>
+        <v>44.3734759808541</v>
       </c>
       <c r="X38" t="n">
         <v>127.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>46.31743268280638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -25553,16 +25553,16 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>64.19144419587266</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>50.7006186397529</v>
+        <v>50.70061863963542</v>
       </c>
       <c r="Q40" t="n">
-        <v>102.243266425598</v>
+        <v>102.2432664254807</v>
       </c>
       <c r="R40" t="n">
-        <v>116.7100624073806</v>
+        <v>180.9015066034881</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25605,10 +25605,10 @@
         <v>159.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>46.26642870806108</v>
+        <v>159.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>28.9694325885074</v>
+        <v>157.9694325885237</v>
       </c>
       <c r="H41" t="n">
         <v>154.9401712663415</v>
@@ -25647,16 +25647,16 @@
         <v>231.8929919229259</v>
       </c>
       <c r="T41" t="n">
-        <v>338.2263756984131</v>
+        <v>209.2263756982153</v>
       </c>
       <c r="U41" t="n">
-        <v>404.1582613727313</v>
+        <v>275.1582613727149</v>
       </c>
       <c r="V41" t="n">
         <v>255.8510241668075</v>
       </c>
       <c r="W41" t="n">
-        <v>264.3734759809311</v>
+        <v>279.7502759811782</v>
       </c>
       <c r="X41" t="n">
         <v>347.2818334606677</v>
@@ -25672,16 +25672,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10.556556646199</v>
+        <v>10.55655664618445</v>
       </c>
       <c r="C42" t="n">
-        <v>116.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>102.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>97.67209722191262</v>
       </c>
       <c r="F42" t="n">
         <v>94.63624233787687</v>
@@ -25690,7 +25690,7 @@
         <v>80.31795096936696</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>83.0964645449117</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25729,10 +25729,10 @@
         <v>158.6584821986459</v>
       </c>
       <c r="U42" t="n">
-        <v>26.1826239109493</v>
+        <v>155.1826239111302</v>
       </c>
       <c r="V42" t="n">
-        <v>107.656028958653</v>
+        <v>40.51066719136389</v>
       </c>
       <c r="W42" t="n">
         <v>187.3731429098285</v>
@@ -25741,7 +25741,7 @@
         <v>174.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>154.3913927661343</v>
+        <v>130.8057921096548</v>
       </c>
     </row>
     <row r="43">
@@ -25754,16 +25754,16 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>27.72524664804467</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>40.53621805555548</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>35.98090483695654</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>29.38285596774193</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -25778,28 +25778,28 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>2.457167243766008</v>
+        <v>2.457167243766001</v>
       </c>
       <c r="L43" t="n">
-        <v>126.0003494692546</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>220.2278736976319</v>
+        <v>220.2278736976318</v>
       </c>
       <c r="N43" t="n">
-        <v>143.0987146159472</v>
+        <v>272.0987146159472</v>
       </c>
       <c r="O43" t="n">
-        <v>345.4880558822937</v>
+        <v>270.7991231326184</v>
       </c>
       <c r="P43" t="n">
-        <v>399.7006186397529</v>
+        <v>270.7006186395417</v>
       </c>
       <c r="Q43" t="n">
-        <v>344.157502295417</v>
+        <v>451.243266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>465.7100624073805</v>
+        <v>465.7100624073806</v>
       </c>
       <c r="S43" t="n">
         <v>111.2139387192489</v>
@@ -25817,10 +25817,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.443645430107551</v>
       </c>
       <c r="Y43" t="n">
-        <v>42.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>236.9993129555745</v>
+        <v>111.999312955539</v>
       </c>
       <c r="C44" t="n">
         <v>204.4745782429939</v>
@@ -25845,7 +25845,7 @@
         <v>159.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>47.86943258852377</v>
+        <v>157.9694325885238</v>
       </c>
       <c r="H44" t="n">
         <v>154.9401712663415</v>
@@ -25881,25 +25881,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>231.8929919229259</v>
+        <v>106.8929919228904</v>
       </c>
       <c r="T44" t="n">
         <v>338.2263756984131</v>
       </c>
       <c r="U44" t="n">
-        <v>279.1582613727313</v>
+        <v>279.1582613726958</v>
       </c>
       <c r="V44" t="n">
-        <v>384.8510241668239</v>
+        <v>274.7510241669304</v>
       </c>
       <c r="W44" t="n">
         <v>393.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>222.2818334606677</v>
+        <v>347.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>141.3174326828064</v>
+        <v>266.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25909,7 +25909,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>139.5565566463266</v>
+        <v>45.96127319654715</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -25918,7 +25918,7 @@
         <v>102.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>97.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -25927,7 +25927,7 @@
         <v>80.31795096936696</v>
       </c>
       <c r="H45" t="n">
-        <v>83.0964645449117</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25966,7 +25966,7 @@
         <v>158.6584821986459</v>
       </c>
       <c r="U45" t="n">
-        <v>30.18262391113014</v>
+        <v>155.1826239111301</v>
       </c>
       <c r="V45" t="n">
         <v>169.5106671915202</v>
@@ -25975,10 +25975,10 @@
         <v>187.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>150.4988942287838</v>
+        <v>174.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>29.39139276613435</v>
+        <v>154.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>35.44505650012406</v>
+        <v>42.11380033707866</v>
       </c>
       <c r="C46" t="n">
         <v>27.72524664804467</v>
@@ -26015,31 +26015,31 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>2.457167243766001</v>
+        <v>2.457167243766008</v>
       </c>
       <c r="L46" t="n">
         <v>126.0003494692546</v>
       </c>
       <c r="M46" t="n">
-        <v>95.22787369763185</v>
+        <v>95.22787369763188</v>
       </c>
       <c r="N46" t="n">
         <v>272.0987146159472</v>
       </c>
       <c r="O46" t="n">
-        <v>345.4880558822936</v>
+        <v>220.4880558822936</v>
       </c>
       <c r="P46" t="n">
-        <v>274.7006186397529</v>
+        <v>399.7006186397529</v>
       </c>
       <c r="Q46" t="n">
         <v>451.243266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>465.7100624073806</v>
+        <v>340.7100624073805</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>75.86590331358299</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26057,7 +26057,7 @@
         <v>2.443645430107551</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>42.46535284946236</v>
       </c>
     </row>
   </sheetData>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>975293.9735843868</v>
+        <v>975293.9735843866</v>
       </c>
     </row>
     <row r="3">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2858238.70528147</v>
+        <v>2858238.705281469</v>
       </c>
     </row>
     <row r="5">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4619133.406495364</v>
+        <v>4619133.406495363</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5579870.13766769</v>
+        <v>5579870.137667689</v>
       </c>
     </row>
     <row r="8">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11139643.28885396</v>
+        <v>11139643.28885395</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12088323.53334331</v>
+        <v>12088323.5333433</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12775920.16191481</v>
+        <v>12775920.1619148</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13461106.62521359</v>
+        <v>13461106.62521358</v>
       </c>
     </row>
   </sheetData>
@@ -26281,13 +26281,13 @@
         <v>1099318.419385279</v>
       </c>
       <c r="F2" t="n">
-        <v>1099318.419385278</v>
+        <v>1099318.41938528</v>
       </c>
       <c r="G2" t="n">
         <v>1208668.790829702</v>
       </c>
       <c r="H2" t="n">
-        <v>1209873.546381701</v>
+        <v>1209873.546381702</v>
       </c>
       <c r="I2" t="n">
         <v>1227892.61432428</v>
@@ -26296,22 +26296,22 @@
         <v>1099600.972786378</v>
       </c>
       <c r="K2" t="n">
-        <v>1099600.972786378</v>
+        <v>1099600.972786379</v>
       </c>
       <c r="L2" t="n">
         <v>1217412.928832659</v>
       </c>
       <c r="M2" t="n">
+        <v>1193500.952744659</v>
+      </c>
+      <c r="N2" t="n">
         <v>1193500.95274466</v>
       </c>
-      <c r="N2" t="n">
-        <v>1193500.952744659</v>
-      </c>
       <c r="O2" t="n">
-        <v>865040.9198157445</v>
+        <v>865040.9198157449</v>
       </c>
       <c r="P2" t="n">
-        <v>863102.6978157447</v>
+        <v>863102.6978157444</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>582227.2078207359</v>
+        <v>582219.8413731204</v>
       </c>
       <c r="C4" t="n">
-        <v>580188.050071653</v>
+        <v>580180.6836240375</v>
       </c>
       <c r="D4" t="n">
-        <v>605717.0639415308</v>
+        <v>605706.6050732387</v>
       </c>
       <c r="E4" t="n">
-        <v>545838.6133645035</v>
+        <v>545826.7968390246</v>
       </c>
       <c r="F4" t="n">
-        <v>544096.6128081323</v>
+        <v>544084.7962826535</v>
       </c>
       <c r="G4" t="n">
-        <v>605315.9923374224</v>
+        <v>605304.1758119436</v>
       </c>
       <c r="H4" t="n">
-        <v>603835.1295023951</v>
+        <v>603823.2239502155</v>
       </c>
       <c r="I4" t="n">
-        <v>609265.0071418529</v>
+        <v>609251.5213657346</v>
       </c>
       <c r="J4" t="n">
-        <v>537112.7865549482</v>
+        <v>537100.8810027685</v>
       </c>
       <c r="K4" t="n">
-        <v>535362.3027345805</v>
+        <v>535350.3971824013</v>
       </c>
       <c r="L4" t="n">
-        <v>604981.3622014384</v>
+        <v>604972.5280704354</v>
       </c>
       <c r="M4" t="n">
-        <v>591480.7049964441</v>
+        <v>591473.2285226278</v>
       </c>
       <c r="N4" t="n">
-        <v>589279.0104119543</v>
+        <v>589271.5339381382</v>
       </c>
       <c r="O4" t="n">
-        <v>404184.936309425</v>
+        <v>404177.459835609</v>
       </c>
       <c r="P4" t="n">
-        <v>401819.8426883493</v>
+        <v>401812.4552412339</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>274052.2263359017</v>
+        <v>274059.5927835171</v>
       </c>
       <c r="C6" t="n">
-        <v>510839.3840849843</v>
+        <v>510846.7505326</v>
       </c>
       <c r="D6" t="n">
-        <v>483212.5263903026</v>
+        <v>483222.9852585946</v>
       </c>
       <c r="E6" t="n">
-        <v>238142.5540207756</v>
+        <v>238154.370546254</v>
       </c>
       <c r="F6" t="n">
-        <v>505356.5545771458</v>
+        <v>505368.3711026261</v>
       </c>
       <c r="G6" t="n">
-        <v>476573.5434922791</v>
+        <v>476585.3600177582</v>
       </c>
       <c r="H6" t="n">
-        <v>547207.9618793065</v>
+        <v>547219.8674314863</v>
       </c>
       <c r="I6" t="n">
-        <v>532148.5591824272</v>
+        <v>532162.0449585455</v>
       </c>
       <c r="J6" t="n">
-        <v>317807.8032314297</v>
+        <v>317819.7087836098</v>
       </c>
       <c r="K6" t="n">
-        <v>514214.2870517978</v>
+        <v>514226.1926039775</v>
       </c>
       <c r="L6" t="n">
-        <v>361162.6816312211</v>
+        <v>361171.5157622241</v>
       </c>
       <c r="M6" t="n">
-        <v>550812.1627482157</v>
+        <v>550819.6392220315</v>
       </c>
       <c r="N6" t="n">
-        <v>553013.8573327046</v>
+        <v>553021.3338065214</v>
       </c>
       <c r="O6" t="n">
-        <v>428143.0785063196</v>
+        <v>428150.5549801359</v>
       </c>
       <c r="P6" t="n">
-        <v>428813.1501273953</v>
+        <v>428820.5375745105</v>
       </c>
     </row>
   </sheetData>
@@ -27533,7 +27533,7 @@
         <v>328.0964645449117</v>
       </c>
       <c r="I3" t="n">
-        <v>91.07586615948195</v>
+        <v>202.6112915517259</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27566,7 +27566,7 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>288.464574607756</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27591,25 +27591,25 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C4" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D4" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E4" t="n">
         <v>400</v>
       </c>
-      <c r="C4" t="n">
-        <v>396.7252466480447</v>
-      </c>
-      <c r="D4" t="n">
-        <v>400</v>
-      </c>
-      <c r="E4" t="n">
-        <v>308.086175068952</v>
-      </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>398.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>244.6904302185792</v>
+        <v>368.6904302185793</v>
       </c>
       <c r="H4" t="n">
-        <v>225.6286998721104</v>
+        <v>349.5995036989659</v>
       </c>
       <c r="I4" t="n">
         <v>166.0044720135609</v>
@@ -27660,7 +27660,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27755,13 +27755,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>223.9376868977026</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>232.8364952513797</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.317950969367</v>
@@ -27770,7 +27770,7 @@
         <v>328.0964645449117</v>
       </c>
       <c r="I6" t="n">
-        <v>202.6112915517259</v>
+        <v>91.07586615948192</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>119.2643216942532</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27840,16 +27840,16 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>398.3828559677419</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
         <v>244.6904302185792</v>
       </c>
       <c r="H7" t="n">
-        <v>349.6286998721104</v>
+        <v>225.6286998721104</v>
       </c>
       <c r="I7" t="n">
-        <v>290.0044720135609</v>
+        <v>166.0044720135609</v>
       </c>
       <c r="J7" t="n">
         <v>10.28055539328483</v>
@@ -27858,7 +27858,7 @@
         <v>247.457167243766</v>
       </c>
       <c r="L7" t="n">
-        <v>371.0003494692546</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,19 +27879,19 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>356.2139387192489</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>208.5144025718315</v>
+        <v>332.5144025718315</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9391125859333</v>
+        <v>274.9391125859333</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>323.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>345.3627088286087</v>
+        <v>272.5769970171121</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27986,16 +27986,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>330.5755100859619</v>
+        <v>121.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>84.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>270.6625415312676</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>119.2643216942532</v>
       </c>
       <c r="R9" t="n">
-        <v>258.0985520093604</v>
+        <v>403</v>
       </c>
       <c r="S9" t="n">
         <v>195.7332452476302</v>
@@ -28052,7 +28052,7 @@
         <v>403</v>
       </c>
       <c r="X9" t="n">
-        <v>403</v>
+        <v>156.8627394453875</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,10 +28065,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>403</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>403</v>
       </c>
       <c r="D10" t="n">
         <v>285.5362180555555</v>
@@ -28077,25 +28077,25 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>403</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>244.6904302185792</v>
       </c>
       <c r="H10" t="n">
-        <v>403</v>
+        <v>225.6286998721104</v>
       </c>
       <c r="I10" t="n">
-        <v>403</v>
+        <v>359.2931772400868</v>
       </c>
       <c r="J10" t="n">
         <v>10.28055539328483</v>
       </c>
       <c r="K10" t="n">
-        <v>247.457167243766</v>
+        <v>403</v>
       </c>
       <c r="L10" t="n">
-        <v>371.0003494692546</v>
+        <v>403</v>
       </c>
       <c r="M10" t="n">
         <v>403</v>
@@ -28116,10 +28116,10 @@
         <v>403</v>
       </c>
       <c r="S10" t="n">
-        <v>356.2139387192489</v>
+        <v>403</v>
       </c>
       <c r="T10" t="n">
-        <v>339.3086332343777</v>
+        <v>208.5144025718315</v>
       </c>
       <c r="U10" t="n">
         <v>403</v>
@@ -28317,7 +28317,7 @@
         <v>308</v>
       </c>
       <c r="G13" t="n">
-        <v>277.6150749880303</v>
+        <v>308</v>
       </c>
       <c r="H13" t="n">
         <v>308</v>
@@ -28326,7 +28326,7 @@
         <v>308</v>
       </c>
       <c r="J13" t="n">
-        <v>308</v>
+        <v>277.6150749880304</v>
       </c>
       <c r="K13" t="n">
         <v>308</v>
@@ -28563,7 +28563,7 @@
         <v>308</v>
       </c>
       <c r="J16" t="n">
-        <v>308</v>
+        <v>277.6150749880304</v>
       </c>
       <c r="K16" t="n">
         <v>308</v>
@@ -28596,7 +28596,7 @@
         <v>308</v>
       </c>
       <c r="U16" t="n">
-        <v>277.6150749880303</v>
+        <v>308</v>
       </c>
       <c r="V16" t="n">
         <v>308</v>
@@ -28706,7 +28706,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>18.67209722191262</v>
       </c>
       <c r="F18" t="n">
         <v>339.6362423378769</v>
@@ -28718,7 +28718,7 @@
         <v>328.0964645449117</v>
       </c>
       <c r="I18" t="n">
-        <v>202.6112915517259</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28751,19 +28751,19 @@
         <v>395</v>
       </c>
       <c r="T18" t="n">
-        <v>79.65848219864588</v>
+        <v>395</v>
       </c>
       <c r="U18" t="n">
-        <v>76.18262391113015</v>
+        <v>258.532270039843</v>
       </c>
       <c r="V18" t="n">
+        <v>90.51066719152016</v>
+      </c>
+      <c r="W18" t="n">
         <v>395</v>
       </c>
-      <c r="W18" t="n">
-        <v>108.3731429098285</v>
-      </c>
       <c r="X18" t="n">
-        <v>348.2173966600329</v>
+        <v>395</v>
       </c>
       <c r="Y18" t="n">
         <v>395</v>
@@ -28779,7 +28779,7 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C19" t="n">
-        <v>395</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D19" t="n">
         <v>285.5362180555555</v>
@@ -28791,16 +28791,16 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G19" t="n">
-        <v>360.4407019948825</v>
+        <v>244.6904302185792</v>
       </c>
       <c r="H19" t="n">
-        <v>395</v>
+        <v>225.6286998721104</v>
       </c>
       <c r="I19" t="n">
-        <v>395</v>
+        <v>166.0044720135609</v>
       </c>
       <c r="J19" t="n">
-        <v>10.28055539328483</v>
+        <v>324.8962170827783</v>
       </c>
       <c r="K19" t="n">
         <v>247.457167243766</v>
@@ -28827,13 +28827,13 @@
         <v>395</v>
       </c>
       <c r="S19" t="n">
-        <v>356.2139387192489</v>
+        <v>395</v>
       </c>
       <c r="T19" t="n">
-        <v>208.5144025718315</v>
+        <v>395</v>
       </c>
       <c r="U19" t="n">
-        <v>150.9391125859333</v>
+        <v>395</v>
       </c>
       <c r="V19" t="n">
         <v>395</v>
@@ -28842,7 +28842,7 @@
         <v>395</v>
       </c>
       <c r="X19" t="n">
-        <v>395</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y19" t="n">
         <v>395</v>
@@ -28937,16 +28937,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>231.4370257657525</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>19.93768689770263</v>
+        <v>20.84613257733986</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>14.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>11.63624233787687</v>
       </c>
       <c r="G21" t="n">
         <v>325.317950969367</v>
@@ -28955,7 +28955,7 @@
         <v>328.0964645449117</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>202.6112915517259</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -28991,7 +28991,7 @@
         <v>395</v>
       </c>
       <c r="U21" t="n">
-        <v>72.18262391113015</v>
+        <v>395</v>
       </c>
       <c r="V21" t="n">
         <v>395</v>
@@ -29016,22 +29016,22 @@
         <v>395</v>
       </c>
       <c r="C22" t="n">
-        <v>272.7252466480447</v>
+        <v>395</v>
       </c>
       <c r="D22" t="n">
-        <v>296.4861316047808</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E22" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F22" t="n">
         <v>395</v>
       </c>
-      <c r="F22" t="n">
-        <v>274.3828559677419</v>
-      </c>
       <c r="G22" t="n">
+        <v>244.6904302185792</v>
+      </c>
+      <c r="H22" t="n">
         <v>395</v>
-      </c>
-      <c r="H22" t="n">
-        <v>225.6286998721104</v>
       </c>
       <c r="I22" t="n">
         <v>395</v>
@@ -29070,10 +29070,10 @@
         <v>208.5144025718315</v>
       </c>
       <c r="U22" t="n">
-        <v>395</v>
+        <v>150.9391125859333</v>
       </c>
       <c r="V22" t="n">
-        <v>199.1703102162162</v>
+        <v>306.2465786118694</v>
       </c>
       <c r="W22" t="n">
         <v>395</v>
@@ -29113,7 +29113,7 @@
         <v>392</v>
       </c>
       <c r="I23" t="n">
-        <v>118.3418788500341</v>
+        <v>119.704114456554</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29149,7 +29149,7 @@
         <v>392</v>
       </c>
       <c r="U23" t="n">
-        <v>392</v>
+        <v>390.6377643934803</v>
       </c>
       <c r="V23" t="n">
         <v>392</v>
@@ -29174,10 +29174,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>86.98279023541249</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -29216,13 +29216,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>119.2643216942532</v>
       </c>
       <c r="R24" t="n">
+        <v>122.0985520093597</v>
+      </c>
+      <c r="S24" t="n">
         <v>392</v>
-      </c>
-      <c r="S24" t="n">
-        <v>59.73324524762952</v>
       </c>
       <c r="T24" t="n">
         <v>392</v>
@@ -29231,13 +29231,13 @@
         <v>392</v>
       </c>
       <c r="V24" t="n">
-        <v>322.7120799027867</v>
+        <v>392</v>
       </c>
       <c r="W24" t="n">
         <v>392</v>
       </c>
       <c r="X24" t="n">
-        <v>20.86273944538689</v>
+        <v>392</v>
       </c>
       <c r="Y24" t="n">
         <v>392</v>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>287.1138003370787</v>
+        <v>392</v>
       </c>
       <c r="C25" t="n">
-        <v>272.7252466480447</v>
+        <v>392</v>
       </c>
       <c r="D25" t="n">
         <v>285.5362180555555</v>
@@ -29271,13 +29271,13 @@
         <v>392</v>
       </c>
       <c r="I25" t="n">
-        <v>392</v>
+        <v>166.0044720135609</v>
       </c>
       <c r="J25" t="n">
-        <v>392</v>
+        <v>10.28055539328483</v>
       </c>
       <c r="K25" t="n">
-        <v>392</v>
+        <v>247.457167243766</v>
       </c>
       <c r="L25" t="n">
         <v>371.0003494692546</v>
@@ -29307,19 +29307,19 @@
         <v>208.5144025718315</v>
       </c>
       <c r="U25" t="n">
-        <v>150.9391125859333</v>
+        <v>303.8542663460065</v>
       </c>
       <c r="V25" t="n">
-        <v>199.1703102162162</v>
+        <v>392</v>
       </c>
       <c r="W25" t="n">
-        <v>226.3728098387097</v>
+        <v>392</v>
       </c>
       <c r="X25" t="n">
         <v>392</v>
       </c>
       <c r="Y25" t="n">
-        <v>375.2751813706358</v>
+        <v>392</v>
       </c>
     </row>
     <row r="26">
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>119.2643216942532</v>
+        <v>119.2643216942644</v>
       </c>
       <c r="R30" t="n">
         <v>307</v>
@@ -29882,16 +29882,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>194.5565566463266</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>157.9376868977026</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>152.6720972219096</v>
       </c>
       <c r="F33" t="n">
         <v>339.6362423378769</v>
@@ -29900,10 +29900,10 @@
         <v>325.317950969367</v>
       </c>
       <c r="H33" t="n">
-        <v>138.0964645449117</v>
+        <v>328.0964645449117</v>
       </c>
       <c r="I33" t="n">
-        <v>91.35784356108641</v>
+        <v>202.6112915517259</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29930,16 +29930,16 @@
         <v>119.2643216942532</v>
       </c>
       <c r="R33" t="n">
-        <v>465</v>
+        <v>331.0985520093574</v>
       </c>
       <c r="S33" t="n">
-        <v>458.7332452476302</v>
+        <v>268.7332452476272</v>
       </c>
       <c r="T33" t="n">
         <v>403.6584821986459</v>
       </c>
       <c r="U33" t="n">
-        <v>400.1826239111301</v>
+        <v>232.8306239111393</v>
       </c>
       <c r="V33" t="n">
         <v>414.5106671915202</v>
@@ -29970,13 +29970,13 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E34" t="n">
-        <v>285.7694900096513</v>
+        <v>465</v>
       </c>
       <c r="F34" t="n">
-        <v>274.3828559677419</v>
+        <v>462.6869931279248</v>
       </c>
       <c r="G34" t="n">
-        <v>434.6904302185793</v>
+        <v>434.6904302185823</v>
       </c>
       <c r="H34" t="n">
         <v>225.6286998721104</v>
@@ -30018,10 +30018,10 @@
         <v>208.5144025718315</v>
       </c>
       <c r="U34" t="n">
-        <v>340.9391125859333</v>
+        <v>340.9391125859364</v>
       </c>
       <c r="V34" t="n">
-        <v>389.1703102162162</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W34" t="n">
         <v>226.3728098387097</v>
@@ -30030,7 +30030,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y34" t="n">
-        <v>465</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="35">
@@ -30134,7 +30134,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>325.317950969367</v>
+        <v>196.3179509693615</v>
       </c>
       <c r="H36" t="n">
         <v>328.0964645449117</v>
@@ -30164,13 +30164,13 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>119.2643216942532</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>465</v>
+        <v>397.7396737036246</v>
       </c>
       <c r="S36" t="n">
-        <v>329.7332452476302</v>
+        <v>458.7332452476302</v>
       </c>
       <c r="T36" t="n">
         <v>403.6584821986459</v>
@@ -30182,13 +30182,13 @@
         <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>374.8484949191944</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>270.3913927661343</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -30204,19 +30204,19 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D37" t="n">
-        <v>414.5362180555555</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E37" t="n">
-        <v>409.9809048369565</v>
+        <v>409.980904836962</v>
       </c>
       <c r="F37" t="n">
-        <v>274.3828559677419</v>
+        <v>403.3828559677474</v>
       </c>
       <c r="G37" t="n">
-        <v>244.6904302185792</v>
+        <v>373.6904302185847</v>
       </c>
       <c r="H37" t="n">
-        <v>354.6286998721104</v>
+        <v>225.6286998721104</v>
       </c>
       <c r="I37" t="n">
         <v>166.0044720135609</v>
@@ -30252,7 +30252,7 @@
         <v>465</v>
       </c>
       <c r="T37" t="n">
-        <v>208.5144025718315</v>
+        <v>223.5162200789427</v>
       </c>
       <c r="U37" t="n">
         <v>150.9391125859333</v>
@@ -30264,7 +30264,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
-        <v>262.4454629372353</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
         <v>287.4653528494624</v>
@@ -30362,19 +30362,19 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>218.9376868977026</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>210.6362423378677</v>
       </c>
       <c r="G39" t="n">
-        <v>325.317950969367</v>
+        <v>196.3179509693579</v>
       </c>
       <c r="H39" t="n">
-        <v>199.0964645449117</v>
+        <v>260.8361382485436</v>
       </c>
       <c r="I39" t="n">
         <v>202.6112915517259</v>
@@ -30401,10 +30401,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.641121694253187</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>392.0985520093604</v>
+        <v>465</v>
       </c>
       <c r="S39" t="n">
         <v>458.7332452476302</v>
@@ -30435,13 +30435,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>410.9016791249575</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C40" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
-        <v>285.5362180555555</v>
+        <v>414.5362180555646</v>
       </c>
       <c r="E40" t="n">
         <v>280.9809048369565</v>
@@ -30453,7 +30453,7 @@
         <v>244.6904302185792</v>
       </c>
       <c r="H40" t="n">
-        <v>354.6286998721104</v>
+        <v>349.4165786599618</v>
       </c>
       <c r="I40" t="n">
         <v>166.0044720135609</v>
@@ -30462,7 +30462,7 @@
         <v>10.28055539328483</v>
       </c>
       <c r="K40" t="n">
-        <v>376.457167243766</v>
+        <v>376.4571672437751</v>
       </c>
       <c r="L40" t="n">
         <v>371.0003494692546</v>
@@ -30492,13 +30492,13 @@
         <v>208.5144025718315</v>
       </c>
       <c r="U40" t="n">
-        <v>279.9391125859333</v>
+        <v>150.9391125859333</v>
       </c>
       <c r="V40" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>355.3728098387188</v>
       </c>
       <c r="X40" t="n">
         <v>247.4436454301076</v>
@@ -30696,7 +30696,7 @@
         <v>245</v>
       </c>
       <c r="J43" t="n">
-        <v>139.2805553932848</v>
+        <v>139.2805553933012</v>
       </c>
       <c r="K43" t="n">
         <v>245</v>
@@ -34752,7 +34752,7 @@
         <v>124</v>
       </c>
       <c r="M2" t="n">
-        <v>59.39786500051696</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -34764,7 +34764,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>59.39786500051702</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,22 +34822,22 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>118.989898989899</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>124</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>124</v>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>124</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>118.989898989899</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -34877,25 +34877,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>119.0190951630435</v>
+      </c>
+      <c r="F4" t="n">
         <v>124</v>
       </c>
-      <c r="D4" t="n">
-        <v>114.4637819444445</v>
-      </c>
-      <c r="E4" t="n">
-        <v>27.10527023199548</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>123.9708038268555</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,7 +34980,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>80.24990926750908</v>
+        <v>31.8323907398343</v>
       </c>
       <c r="K5" t="n">
         <v>100.2288844221106</v>
@@ -34998,10 +34998,10 @@
         <v>62.51110530027941</v>
       </c>
       <c r="P5" t="n">
-        <v>124</v>
+        <v>113.0196535271578</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>59.39786500051702</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,19 +35059,19 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>124</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>124</v>
+      </c>
+      <c r="N6" t="n">
         <v>118.989898989899</v>
-      </c>
-      <c r="K6" t="n">
-        <v>124</v>
-      </c>
-      <c r="L6" t="n">
-        <v>124</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -35126,58 +35126,58 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>28.99965053074542</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>43.78606128075112</v>
+      </c>
+      <c r="T7" t="n">
         <v>124</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="U7" t="n">
         <v>124</v>
       </c>
-      <c r="I7" t="n">
+      <c r="V7" t="n">
         <v>124</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
-        <v>118.989898989899</v>
+        <v>46.20418717840248</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -35220,7 +35220,7 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K8" t="n">
-        <v>183.6677938366167</v>
+        <v>100.2288844221106</v>
       </c>
       <c r="L8" t="n">
         <v>124.3427939698493</v>
@@ -35238,7 +35238,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>83.43890941450614</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,22 +35296,22 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>165.0391345395625</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>259.1805716219234</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="M9" t="n">
-        <v>193.7700421645043</v>
+        <v>76.92974878816511</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>244.2737576558247</v>
       </c>
       <c r="O9" t="n">
-        <v>229.2137581179998</v>
+        <v>263</v>
       </c>
       <c r="P9" t="n">
         <v>194.1702309297476</v>
@@ -35351,10 +35351,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>115.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>130.2747533519553</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -35363,25 +35363,25 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>128.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>177.3713001278896</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>236.9955279864391</v>
+        <v>193.2887052265258</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>155.542832756234</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>31.99965053074542</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,10 +35402,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>46.78606128075112</v>
       </c>
       <c r="T10" t="n">
-        <v>130.7942306625462</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>252.0608874140667</v>
@@ -35454,22 +35454,22 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>31.8323907398343</v>
+        <v>324</v>
       </c>
       <c r="K11" t="n">
-        <v>100.2288844221106</v>
+        <v>100.2288844221105</v>
       </c>
       <c r="L11" t="n">
+        <v>124.3427939698493</v>
+      </c>
+      <c r="M11" t="n">
         <v>324</v>
       </c>
-      <c r="M11" t="n">
-        <v>324.0000000000006</v>
-      </c>
       <c r="N11" t="n">
-        <v>324.0000000000006</v>
+        <v>234.8066536896941</v>
       </c>
       <c r="O11" t="n">
-        <v>65.82816221998725</v>
+        <v>62.51110530027941</v>
       </c>
       <c r="P11" t="n">
         <v>113.0196535271578</v>
@@ -35536,10 +35536,10 @@
         <v>165.0391345395625</v>
       </c>
       <c r="K12" t="n">
-        <v>161.6559256194519</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="M12" t="n">
         <v>193.7700421645043</v>
@@ -35551,7 +35551,7 @@
         <v>324</v>
       </c>
       <c r="P12" t="n">
-        <v>194.1702309297476</v>
+        <v>31.8261565491995</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -35603,7 +35603,7 @@
         <v>33.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>32.92464476945104</v>
+        <v>63.30956978142078</v>
       </c>
       <c r="H13" t="n">
         <v>82.37130012788958</v>
@@ -35612,10 +35612,10 @@
         <v>141.9955279864391</v>
       </c>
       <c r="J13" t="n">
-        <v>297.7194446067152</v>
+        <v>267.3345195947455</v>
       </c>
       <c r="K13" t="n">
-        <v>60.542832756234</v>
+        <v>60.54283275623399</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>31.8323907398343</v>
+        <v>324</v>
       </c>
       <c r="K14" t="n">
-        <v>303.2031473719691</v>
+        <v>100.2288844221105</v>
       </c>
       <c r="L14" t="n">
         <v>124.3427939698493</v>
       </c>
       <c r="M14" t="n">
-        <v>324.0000000000006</v>
+        <v>324</v>
       </c>
       <c r="N14" t="n">
-        <v>324.0000000000006</v>
+        <v>234.8066536896941</v>
       </c>
       <c r="O14" t="n">
         <v>62.51110530027941</v>
@@ -35776,7 +35776,7 @@
         <v>259.1805716219234</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>226.4753539975286</v>
       </c>
       <c r="M15" t="n">
         <v>193.7700421645043</v>
@@ -35785,7 +35785,7 @@
         <v>244.2737576558247</v>
       </c>
       <c r="O15" t="n">
-        <v>226.4753539975285</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>194.1702309297476</v>
@@ -35840,7 +35840,7 @@
         <v>33.61714403225807</v>
       </c>
       <c r="G16" t="n">
-        <v>63.30956978142078</v>
+        <v>63.30956978142079</v>
       </c>
       <c r="H16" t="n">
         <v>82.37130012788958</v>
@@ -35849,10 +35849,10 @@
         <v>141.9955279864391</v>
       </c>
       <c r="J16" t="n">
-        <v>297.7194446067152</v>
+        <v>267.3345195947455</v>
       </c>
       <c r="K16" t="n">
-        <v>60.54283275623399</v>
+        <v>60.542832756234</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35882,7 +35882,7 @@
         <v>99.48559742816852</v>
       </c>
       <c r="U16" t="n">
-        <v>126.675962402097</v>
+        <v>157.0608874140667</v>
       </c>
       <c r="V16" t="n">
         <v>108.8296897837838</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>234.8066536896928</v>
+        <v>324</v>
       </c>
       <c r="K17" t="n">
-        <v>100.2288844221106</v>
+        <v>100.2288844221105</v>
       </c>
       <c r="L17" t="n">
         <v>124.3427939698493</v>
       </c>
       <c r="M17" t="n">
-        <v>324.0000000000006</v>
+        <v>324</v>
       </c>
       <c r="N17" t="n">
-        <v>324.0000000000006</v>
+        <v>234.8066536896941</v>
       </c>
       <c r="O17" t="n">
         <v>62.51110530027941</v>
@@ -36010,13 +36010,13 @@
         <v>165.0391345395625</v>
       </c>
       <c r="K18" t="n">
-        <v>259.1805716219234</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="M18" t="n">
-        <v>96.24539616203282</v>
+        <v>193.7700421645043</v>
       </c>
       <c r="N18" t="n">
         <v>244.2737576558247</v>
@@ -36025,7 +36025,7 @@
         <v>324</v>
       </c>
       <c r="P18" t="n">
-        <v>194.1702309297476</v>
+        <v>31.8261565491995</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -36065,7 +36065,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>122.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -36077,16 +36077,16 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>115.7502717763033</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>169.3713001278896</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>228.9955279864391</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>314.6156616894934</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -36113,13 +36113,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>38.78606128075114</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>186.4855974281685</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>244.0608874140667</v>
       </c>
       <c r="V19" t="n">
         <v>195.8296897837838</v>
@@ -36128,7 +36128,7 @@
         <v>168.6271901612903</v>
       </c>
       <c r="X19" t="n">
-        <v>147.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>107.5346471505376</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>328.0000000000005</v>
+        <v>31.8323907398343</v>
       </c>
       <c r="K20" t="n">
         <v>100.2288844221106</v>
       </c>
       <c r="L20" t="n">
-        <v>124.3427939698493</v>
+        <v>124.3427939698492</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>328.0000000000005</v>
       </c>
       <c r="N20" t="n">
         <v>328.0000000000005</v>
       </c>
       <c r="O20" t="n">
-        <v>305.1561428283561</v>
+        <v>62.51110530027941</v>
       </c>
       <c r="P20" t="n">
         <v>113.0196535271578</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>210.8126467882426</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36244,22 +36244,22 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>165.0391345395625</v>
       </c>
       <c r="K21" t="n">
         <v>259.1805716219234</v>
       </c>
       <c r="L21" t="n">
-        <v>323.6266300312996</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>193.7700421645043</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>244.2737576558247</v>
       </c>
       <c r="O21" t="n">
-        <v>328</v>
+        <v>242.3137378359124</v>
       </c>
       <c r="P21" t="n">
         <v>194.1702309297476</v>
@@ -36302,22 +36302,22 @@
         <v>107.8861996629213</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>122.2747533519553</v>
       </c>
       <c r="D22" t="n">
-        <v>10.94991354922538</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>114.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>120.6171440322581</v>
       </c>
       <c r="G22" t="n">
-        <v>150.3095697814208</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>169.3713001278896</v>
       </c>
       <c r="I22" t="n">
         <v>228.9955279864391</v>
@@ -36356,10 +36356,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>244.0608874140667</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>107.0762683956532</v>
       </c>
       <c r="W22" t="n">
         <v>168.6271901612903</v>
@@ -36405,22 +36405,22 @@
         <v>399.0000000000007</v>
       </c>
       <c r="K23" t="n">
-        <v>100.2288844221105</v>
+        <v>398.9999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>220.1387981563959</v>
+        <v>124.3427939698493</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>83.00523508150016</v>
       </c>
       <c r="O23" t="n">
         <v>62.51110530027941</v>
       </c>
       <c r="P23" t="n">
-        <v>399.0000000000007</v>
+        <v>113.0196535271578</v>
       </c>
       <c r="Q23" t="n">
         <v>399.0000000000007</v>
@@ -36481,16 +36481,16 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>165.0391345395625</v>
       </c>
       <c r="K24" t="n">
-        <v>240.273039122561</v>
+        <v>259.1805716219234</v>
       </c>
       <c r="L24" t="n">
         <v>365.6289225184984</v>
       </c>
       <c r="M24" t="n">
-        <v>193.7700421645043</v>
+        <v>9.823375125579378</v>
       </c>
       <c r="N24" t="n">
         <v>244.2737576558247</v>
@@ -36536,10 +36536,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>104.8861996629213</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>119.2747533519553</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -36557,13 +36557,13 @@
         <v>166.3713001278896</v>
       </c>
       <c r="I25" t="n">
-        <v>225.9955279864391</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>381.7194446067152</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>144.542832756234</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36593,19 +36593,19 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>152.9151537600732</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>192.8296897837838</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>165.6271901612903</v>
       </c>
       <c r="X25" t="n">
         <v>144.5563545698924</v>
       </c>
       <c r="Y25" t="n">
-        <v>87.80982852117339</v>
+        <v>104.5346471505376</v>
       </c>
     </row>
     <row r="26">
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>328.0000000000001</v>
+        <v>31.8323907398343</v>
       </c>
       <c r="K26" t="n">
         <v>100.2288844221106</v>
       </c>
       <c r="L26" t="n">
-        <v>328</v>
+        <v>124.3427939698492</v>
       </c>
       <c r="M26" t="n">
         <v>328.0000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>328.0000000000001</v>
       </c>
       <c r="O26" t="n">
         <v>62.51110530027941</v>
@@ -36660,7 +36660,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q26" t="n">
-        <v>38.98783149792705</v>
+        <v>210.8126467882435</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36718,13 +36718,13 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>165.0391345395625</v>
       </c>
       <c r="K27" t="n">
-        <v>204.7036749271459</v>
+        <v>173.4943094578358</v>
       </c>
       <c r="L27" t="n">
-        <v>328</v>
+        <v>328.0000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>193.7700421645043</v>
@@ -36733,10 +36733,10 @@
         <v>244.2737576558247</v>
       </c>
       <c r="O27" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>194.1702309297476</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
+        <v>31.8323907398343</v>
+      </c>
+      <c r="K29" t="n">
+        <v>100.2288844221106</v>
+      </c>
+      <c r="L29" t="n">
+        <v>124.3427939698492</v>
+      </c>
+      <c r="M29" t="n">
         <v>328.000000000001</v>
       </c>
-      <c r="K29" t="n">
-        <v>328</v>
-      </c>
-      <c r="L29" t="n">
-        <v>124.3427939698493</v>
-      </c>
-      <c r="M29" t="n">
-        <v>127.8935754773441</v>
-      </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>328.000000000001</v>
       </c>
       <c r="O29" t="n">
         <v>62.51110530027941</v>
       </c>
       <c r="P29" t="n">
-        <v>328.000000000001</v>
+        <v>113.0196535271578</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>210.8126467882417</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36961,22 +36961,22 @@
         <v>259.1805716219234</v>
       </c>
       <c r="L30" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>24.35753765624126</v>
+        <v>108.0837800004157</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>244.2737576558247</v>
       </c>
       <c r="O30" t="n">
-        <v>328</v>
+        <v>328.000000000001</v>
       </c>
       <c r="P30" t="n">
         <v>194.1702309297476</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.125384858254381e-11</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37128,13 +37128,13 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>190.000000000003</v>
+        <v>62.51110530027941</v>
       </c>
       <c r="P32" t="n">
-        <v>115.9191631914321</v>
+        <v>113.0196535271578</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>130.388404363998</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37195,22 +37195,22 @@
         <v>165.0391345395625</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>190.000000000003</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>190.000000000003</v>
       </c>
       <c r="M33" t="n">
-        <v>190</v>
+        <v>17.28409778366076</v>
       </c>
       <c r="N33" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>17.28409778366984</v>
+        <v>190.000000000003</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37256,13 +37256,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>4.78858517269474</v>
+        <v>184.0190951630435</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>188.3041371601828</v>
       </c>
       <c r="G34" t="n">
-        <v>190</v>
+        <v>190.000000000003</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -37304,10 +37304,10 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>190</v>
+        <v>190.000000000003</v>
       </c>
       <c r="V34" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -37316,7 +37316,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>177.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -37359,7 +37359,7 @@
         <v>124.3427939698492</v>
       </c>
       <c r="M35" t="n">
-        <v>78.85305082864747</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -37371,7 +37371,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>78.85305082864753</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37429,22 +37429,22 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>129.0000000000055</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>123.7878787878623</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>129.0000000000055</v>
       </c>
       <c r="O36" t="n">
-        <v>129.0000000000055</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>129.0000000000055</v>
@@ -37490,19 +37490,19 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>129</v>
+        <v>129.0000000000055</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>129.0000000000055</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>129.0000000000055</v>
       </c>
       <c r="H37" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -37538,7 +37538,7 @@
         <v>108.7860612807511</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>15.00181750711117</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -37550,7 +37550,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>15.00181750712771</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -37596,10 +37596,10 @@
         <v>124.3427939698492</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>78.85305082864747</v>
       </c>
       <c r="N38" t="n">
-        <v>78.85305082864747</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>62.51110530027941</v>
@@ -37666,22 +37666,22 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="L39" t="n">
         <v>129.0000000000091</v>
       </c>
       <c r="M39" t="n">
-        <v>123.7878787878606</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>129.0000000000091</v>
+        <v>123.7878787878514</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -37721,13 +37721,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>123.7878787878788</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -37739,7 +37739,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>129</v>
+        <v>123.7878787878514</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -37748,7 +37748,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>129</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37778,13 +37778,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -37824,16 +37824,16 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>81.91432599059235</v>
+        <v>31.8323907398343</v>
       </c>
       <c r="K41" t="n">
-        <v>129</v>
+        <v>100.2288844221106</v>
       </c>
       <c r="L41" t="n">
-        <v>124.3427939698493</v>
+        <v>124.3427939698492</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>78.85305082864747</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -37903,25 +37903,25 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>129.0000000000164</v>
       </c>
       <c r="K42" t="n">
-        <v>123.787878787846</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
         <v>129.0000000000164</v>
       </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>129</v>
-      </c>
       <c r="O42" t="n">
+        <v>123.7878787878296</v>
+      </c>
+      <c r="P42" t="n">
         <v>129.0000000000164</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37973,7 +37973,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3095697814207767</v>
+        <v>0.3095697814207878</v>
       </c>
       <c r="H43" t="n">
         <v>19.37130012788958</v>
@@ -37982,7 +37982,7 @@
         <v>78.9955279864391</v>
       </c>
       <c r="J43" t="n">
-        <v>129</v>
+        <v>129.0000000000164</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38146,19 +38146,19 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>119.949494949424</v>
       </c>
       <c r="N45" t="n">
         <v>125</v>
       </c>
       <c r="O45" t="n">
-        <v>125</v>
+        <v>125.0000000000355</v>
       </c>
       <c r="P45" t="n">
-        <v>119.9494949494949</v>
+        <v>125.0000000000355</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -38210,7 +38210,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3095697814207878</v>
+        <v>0.3095697814207767</v>
       </c>
       <c r="H46" t="n">
         <v>19.37130012788958</v>
